--- a/CryoGrid/CryoGridCommunity_results/templates/restart_broken/restart_broken.xlsx
+++ b/CryoGrid/CryoGridCommunity_results/templates/restart_broken/restart_broken.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="503" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="573" uniqueCount="223">
   <si>
     <t>-------------------</t>
   </si>
@@ -430,7 +430,7 @@
     <t>..\CryoGridCommunity_results\templates\restart_broken\</t>
   </si>
   <si>
-    <t>restart_broken_tile1_run1_19590902_last_timestep</t>
+    <t>restart_broken_tile1_run1_19580830_last_timestep</t>
   </si>
   <si>
     <t>update_forcing_out</t>
@@ -443,6 +443,9 @@
   </si>
   <si>
     <t>restart_broken_tile7_run1_19590902_last_timestep</t>
+  </si>
+  <si>
+    <t>restart_broken_tile9_run1_19590902_last_timestep</t>
   </si>
   <si>
     <t>FORCING_data_01Aug1958_01Aug2024_MON1</t>
@@ -725,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L342"/>
+  <dimension ref="A1:N389"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.453125" customWidth="true"/>
@@ -739,7 +742,9 @@
     <col min="9" max="9" width="7.54296875" customWidth="true"/>
     <col min="10" max="10" width="39.36328125" customWidth="true"/>
     <col min="11" max="11" width="7.54296875" customWidth="true"/>
-    <col min="12" max="12" width="4.453125" customWidth="true"/>
+    <col min="12" max="12" width="7.54296875" customWidth="true"/>
+    <col min="13" max="13" width="7.54296875" customWidth="true"/>
+    <col min="14" max="14" width="4.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -757,6 +762,8 @@
       <c r="J1" s="0"/>
       <c r="K1" s="0"/>
       <c r="L1" s="0"/>
+      <c r="M1" s="0"/>
+      <c r="N1" s="0"/>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -775,6 +782,8 @@
       <c r="J2" s="0"/>
       <c r="K2" s="0"/>
       <c r="L2" s="0"/>
+      <c r="M2" s="0"/>
+      <c r="N2" s="0"/>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
@@ -793,6 +802,8 @@
       <c r="J3" s="0"/>
       <c r="K3" s="0"/>
       <c r="L3" s="0"/>
+      <c r="M3" s="0"/>
+      <c r="N3" s="0"/>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
@@ -811,6 +822,8 @@
       <c r="J4" s="0"/>
       <c r="K4" s="0"/>
       <c r="L4" s="0"/>
+      <c r="M4" s="0"/>
+      <c r="N4" s="0"/>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
@@ -829,6 +842,8 @@
       <c r="J5" s="0"/>
       <c r="K5" s="0"/>
       <c r="L5" s="0"/>
+      <c r="M5" s="0"/>
+      <c r="N5" s="0"/>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
@@ -865,7 +880,13 @@
         <v>20</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>147</v>
+        <v>20</v>
+      </c>
+      <c r="M6" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="N6" s="0" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="7">
@@ -902,8 +923,14 @@
       <c r="K7" s="0">
         <v>9</v>
       </c>
-      <c r="L7" s="0" t="s">
-        <v>147</v>
+      <c r="L7" s="0">
+        <v>10</v>
+      </c>
+      <c r="M7" s="0">
+        <v>11</v>
+      </c>
+      <c r="N7" s="0" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="8">
@@ -940,8 +967,14 @@
       <c r="K8" s="0">
         <v>1</v>
       </c>
-      <c r="L8" s="0" t="s">
-        <v>147</v>
+      <c r="L8" s="0">
+        <v>1</v>
+      </c>
+      <c r="M8" s="0">
+        <v>1</v>
+      </c>
+      <c r="N8" s="0" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="9">
@@ -959,6 +992,8 @@
       <c r="J9" s="0"/>
       <c r="K9" s="0"/>
       <c r="L9" s="0"/>
+      <c r="M9" s="0"/>
+      <c r="N9" s="0"/>
     </row>
     <row r="10">
       <c r="A10" s="0"/>
@@ -973,6 +1008,8 @@
       <c r="J10" s="0"/>
       <c r="K10" s="0"/>
       <c r="L10" s="0"/>
+      <c r="M10" s="0"/>
+      <c r="N10" s="0"/>
     </row>
     <row r="11">
       <c r="A11" s="0"/>
@@ -987,6 +1024,8 @@
       <c r="J11" s="0"/>
       <c r="K11" s="0"/>
       <c r="L11" s="0"/>
+      <c r="M11" s="0"/>
+      <c r="N11" s="0"/>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
@@ -1003,6 +1042,8 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0"/>
+      <c r="M12" s="0"/>
+      <c r="N12" s="0"/>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
@@ -1021,6 +1062,8 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0"/>
+      <c r="M13" s="0"/>
+      <c r="N13" s="0"/>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
@@ -1039,6 +1082,8 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0"/>
+      <c r="M14" s="0"/>
+      <c r="N14" s="0"/>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
@@ -1057,6 +1102,8 @@
       <c r="J15" s="0"/>
       <c r="K15" s="0"/>
       <c r="L15" s="0"/>
+      <c r="M15" s="0"/>
+      <c r="N15" s="0"/>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
@@ -1075,6 +1122,8 @@
       <c r="J16" s="0"/>
       <c r="K16" s="0"/>
       <c r="L16" s="0"/>
+      <c r="M16" s="0"/>
+      <c r="N16" s="0"/>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
@@ -1093,6 +1142,8 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0"/>
+      <c r="M17" s="0"/>
+      <c r="N17" s="0"/>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
@@ -1111,6 +1162,8 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0"/>
+      <c r="M18" s="0"/>
+      <c r="N18" s="0"/>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
@@ -1129,6 +1182,8 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0"/>
+      <c r="M19" s="0"/>
+      <c r="N19" s="0"/>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
@@ -1147,6 +1202,8 @@
       <c r="J20" s="0"/>
       <c r="K20" s="0"/>
       <c r="L20" s="0"/>
+      <c r="M20" s="0"/>
+      <c r="N20" s="0"/>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
@@ -1165,6 +1222,8 @@
       <c r="J21" s="0"/>
       <c r="K21" s="0"/>
       <c r="L21" s="0"/>
+      <c r="M21" s="0"/>
+      <c r="N21" s="0"/>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
@@ -1181,6 +1240,8 @@
       <c r="J22" s="0"/>
       <c r="K22" s="0"/>
       <c r="L22" s="0"/>
+      <c r="M22" s="0"/>
+      <c r="N22" s="0"/>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
@@ -1197,6 +1258,8 @@
       <c r="J23" s="0"/>
       <c r="K23" s="0"/>
       <c r="L23" s="0"/>
+      <c r="M23" s="0"/>
+      <c r="N23" s="0"/>
     </row>
     <row r="24">
       <c r="A24" s="0"/>
@@ -1211,6 +1274,8 @@
       <c r="J24" s="0"/>
       <c r="K24" s="0"/>
       <c r="L24" s="0"/>
+      <c r="M24" s="0"/>
+      <c r="N24" s="0"/>
     </row>
     <row r="25">
       <c r="A25" s="0"/>
@@ -1225,6 +1290,8 @@
       <c r="J25" s="0"/>
       <c r="K25" s="0"/>
       <c r="L25" s="0"/>
+      <c r="M25" s="0"/>
+      <c r="N25" s="0"/>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
@@ -1241,6 +1308,8 @@
       <c r="J26" s="0"/>
       <c r="K26" s="0"/>
       <c r="L26" s="0"/>
+      <c r="M26" s="0"/>
+      <c r="N26" s="0"/>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
@@ -1259,6 +1328,8 @@
       <c r="J27" s="0"/>
       <c r="K27" s="0"/>
       <c r="L27" s="0"/>
+      <c r="M27" s="0"/>
+      <c r="N27" s="0"/>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
@@ -1277,6 +1348,8 @@
       <c r="J28" s="0"/>
       <c r="K28" s="0"/>
       <c r="L28" s="0"/>
+      <c r="M28" s="0"/>
+      <c r="N28" s="0"/>
     </row>
     <row r="29">
       <c r="A29" s="0"/>
@@ -1291,6 +1364,8 @@
       <c r="J29" s="0"/>
       <c r="K29" s="0"/>
       <c r="L29" s="0"/>
+      <c r="M29" s="0"/>
+      <c r="N29" s="0"/>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
@@ -1309,6 +1384,8 @@
       <c r="J30" s="0"/>
       <c r="K30" s="0"/>
       <c r="L30" s="0"/>
+      <c r="M30" s="0"/>
+      <c r="N30" s="0"/>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
@@ -1318,7 +1395,7 @@
         <v>100</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D31" s="0"/>
       <c r="E31" s="0"/>
@@ -1329,6 +1406,8 @@
       <c r="J31" s="0"/>
       <c r="K31" s="0"/>
       <c r="L31" s="0"/>
+      <c r="M31" s="0"/>
+      <c r="N31" s="0"/>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
@@ -1347,6 +1426,8 @@
       <c r="J32" s="0"/>
       <c r="K32" s="0"/>
       <c r="L32" s="0"/>
+      <c r="M32" s="0"/>
+      <c r="N32" s="0"/>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
@@ -1365,6 +1446,8 @@
       <c r="J33" s="0"/>
       <c r="K33" s="0"/>
       <c r="L33" s="0"/>
+      <c r="M33" s="0"/>
+      <c r="N33" s="0"/>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
@@ -1383,6 +1466,8 @@
       <c r="J34" s="0"/>
       <c r="K34" s="0"/>
       <c r="L34" s="0"/>
+      <c r="M34" s="0"/>
+      <c r="N34" s="0"/>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
@@ -1401,6 +1486,8 @@
       <c r="J35" s="0"/>
       <c r="K35" s="0"/>
       <c r="L35" s="0"/>
+      <c r="M35" s="0"/>
+      <c r="N35" s="0"/>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
@@ -1413,7 +1500,7 @@
         <v>63</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E36" s="0"/>
       <c r="F36" s="0"/>
@@ -1423,6 +1510,8 @@
       <c r="J36" s="0"/>
       <c r="K36" s="0"/>
       <c r="L36" s="0"/>
+      <c r="M36" s="0"/>
+      <c r="N36" s="0"/>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
@@ -1435,7 +1524,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E37" s="0"/>
       <c r="F37" s="0"/>
@@ -1445,6 +1534,8 @@
       <c r="J37" s="0"/>
       <c r="K37" s="0"/>
       <c r="L37" s="0"/>
+      <c r="M37" s="0"/>
+      <c r="N37" s="0"/>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
@@ -1463,6 +1554,8 @@
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
       <c r="L38" s="0"/>
+      <c r="M38" s="0"/>
+      <c r="N38" s="0"/>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
@@ -1481,6 +1574,8 @@
       <c r="J39" s="0"/>
       <c r="K39" s="0"/>
       <c r="L39" s="0"/>
+      <c r="M39" s="0"/>
+      <c r="N39" s="0"/>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
@@ -1496,10 +1591,10 @@
         <v>82</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G40" s="0"/>
       <c r="H40" s="0"/>
@@ -1507,6 +1602,8 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
       <c r="L40" s="0"/>
+      <c r="M40" s="0"/>
+      <c r="N40" s="0"/>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
@@ -1522,7 +1619,7 @@
         <v>1</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F41" s="0"/>
       <c r="G41" s="0"/>
@@ -1531,6 +1628,8 @@
       <c r="J41" s="0"/>
       <c r="K41" s="0"/>
       <c r="L41" s="0"/>
+      <c r="M41" s="0"/>
+      <c r="N41" s="0"/>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
@@ -1540,7 +1639,7 @@
         <v>118</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D42" s="0"/>
       <c r="E42" s="0"/>
@@ -1551,6 +1650,8 @@
       <c r="J42" s="0"/>
       <c r="K42" s="0"/>
       <c r="L42" s="0"/>
+      <c r="M42" s="0"/>
+      <c r="N42" s="0"/>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
@@ -1569,6 +1670,8 @@
       <c r="J43" s="0"/>
       <c r="K43" s="0"/>
       <c r="L43" s="0"/>
+      <c r="M43" s="0"/>
+      <c r="N43" s="0"/>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
@@ -1581,10 +1684,10 @@
         <v>121</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F44" s="0"/>
       <c r="G44" s="0"/>
@@ -1593,6 +1696,8 @@
       <c r="J44" s="0"/>
       <c r="K44" s="0"/>
       <c r="L44" s="0"/>
+      <c r="M44" s="0"/>
+      <c r="N44" s="0"/>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
@@ -1605,7 +1710,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E45" s="0"/>
       <c r="F45" s="0"/>
@@ -1615,6 +1720,8 @@
       <c r="J45" s="0"/>
       <c r="K45" s="0"/>
       <c r="L45" s="0"/>
+      <c r="M45" s="0"/>
+      <c r="N45" s="0"/>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
@@ -1622,7 +1729,7 @@
       </c>
       <c r="B46" s="0"/>
       <c r="C46" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D46" s="0"/>
       <c r="E46" s="0"/>
@@ -1633,6 +1740,8 @@
       <c r="J46" s="0"/>
       <c r="K46" s="0"/>
       <c r="L46" s="0"/>
+      <c r="M46" s="0"/>
+      <c r="N46" s="0"/>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
@@ -1649,6 +1758,8 @@
       <c r="J47" s="0"/>
       <c r="K47" s="0"/>
       <c r="L47" s="0"/>
+      <c r="M47" s="0"/>
+      <c r="N47" s="0"/>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
@@ -1667,6 +1778,8 @@
       <c r="J48" s="0"/>
       <c r="K48" s="0"/>
       <c r="L48" s="0"/>
+      <c r="M48" s="0"/>
+      <c r="N48" s="0"/>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
@@ -1676,7 +1789,7 @@
         <v>0.5</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D49" s="0"/>
       <c r="E49" s="0"/>
@@ -1687,6 +1800,8 @@
       <c r="J49" s="0"/>
       <c r="K49" s="0"/>
       <c r="L49" s="0"/>
+      <c r="M49" s="0"/>
+      <c r="N49" s="0"/>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
@@ -1703,6 +1818,8 @@
       <c r="J50" s="0"/>
       <c r="K50" s="0"/>
       <c r="L50" s="0"/>
+      <c r="M50" s="0"/>
+      <c r="N50" s="0"/>
     </row>
     <row r="51">
       <c r="A51" s="0"/>
@@ -1717,6 +1834,8 @@
       <c r="J51" s="0"/>
       <c r="K51" s="0"/>
       <c r="L51" s="0"/>
+      <c r="M51" s="0"/>
+      <c r="N51" s="0"/>
     </row>
     <row r="52">
       <c r="A52" s="0"/>
@@ -1731,6 +1850,8 @@
       <c r="J52" s="0"/>
       <c r="K52" s="0"/>
       <c r="L52" s="0"/>
+      <c r="M52" s="0"/>
+      <c r="N52" s="0"/>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
@@ -1747,6 +1868,8 @@
       <c r="J53" s="0"/>
       <c r="K53" s="0"/>
       <c r="L53" s="0"/>
+      <c r="M53" s="0"/>
+      <c r="N53" s="0"/>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
@@ -1765,6 +1888,8 @@
       <c r="J54" s="0"/>
       <c r="K54" s="0"/>
       <c r="L54" s="0"/>
+      <c r="M54" s="0"/>
+      <c r="N54" s="0"/>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
@@ -1783,6 +1908,8 @@
       <c r="J55" s="0"/>
       <c r="K55" s="0"/>
       <c r="L55" s="0"/>
+      <c r="M55" s="0"/>
+      <c r="N55" s="0"/>
     </row>
     <row r="56">
       <c r="A56" s="0"/>
@@ -1797,6 +1924,8 @@
       <c r="J56" s="0"/>
       <c r="K56" s="0"/>
       <c r="L56" s="0"/>
+      <c r="M56" s="0"/>
+      <c r="N56" s="0"/>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
@@ -1815,6 +1944,8 @@
       <c r="J57" s="0"/>
       <c r="K57" s="0"/>
       <c r="L57" s="0"/>
+      <c r="M57" s="0"/>
+      <c r="N57" s="0"/>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
@@ -1833,6 +1964,8 @@
       <c r="J58" s="0"/>
       <c r="K58" s="0"/>
       <c r="L58" s="0"/>
+      <c r="M58" s="0"/>
+      <c r="N58" s="0"/>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
@@ -1851,6 +1984,8 @@
       <c r="J59" s="0"/>
       <c r="K59" s="0"/>
       <c r="L59" s="0"/>
+      <c r="M59" s="0"/>
+      <c r="N59" s="0"/>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
@@ -1863,7 +1998,7 @@
         <v>61</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E60" s="0"/>
       <c r="F60" s="0"/>
@@ -1873,6 +2008,8 @@
       <c r="J60" s="0"/>
       <c r="K60" s="0"/>
       <c r="L60" s="0"/>
+      <c r="M60" s="0"/>
+      <c r="N60" s="0"/>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
@@ -1885,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E61" s="0"/>
       <c r="F61" s="0"/>
@@ -1895,6 +2032,8 @@
       <c r="J61" s="0"/>
       <c r="K61" s="0"/>
       <c r="L61" s="0"/>
+      <c r="M61" s="0"/>
+      <c r="N61" s="0"/>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
@@ -1911,6 +2050,8 @@
       <c r="J62" s="0"/>
       <c r="K62" s="0"/>
       <c r="L62" s="0"/>
+      <c r="M62" s="0"/>
+      <c r="N62" s="0"/>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
@@ -1927,6 +2068,8 @@
       <c r="J63" s="0"/>
       <c r="K63" s="0"/>
       <c r="L63" s="0"/>
+      <c r="M63" s="0"/>
+      <c r="N63" s="0"/>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
@@ -1943,6 +2086,8 @@
       <c r="J64" s="0"/>
       <c r="K64" s="0"/>
       <c r="L64" s="0"/>
+      <c r="M64" s="0"/>
+      <c r="N64" s="0"/>
     </row>
     <row r="65">
       <c r="A65" s="0"/>
@@ -1957,6 +2102,8 @@
       <c r="J65" s="0"/>
       <c r="K65" s="0"/>
       <c r="L65" s="0"/>
+      <c r="M65" s="0"/>
+      <c r="N65" s="0"/>
     </row>
     <row r="66">
       <c r="A66" s="0"/>
@@ -1971,6 +2118,8 @@
       <c r="J66" s="0"/>
       <c r="K66" s="0"/>
       <c r="L66" s="0"/>
+      <c r="M66" s="0"/>
+      <c r="N66" s="0"/>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
@@ -1987,6 +2136,8 @@
       <c r="J67" s="0"/>
       <c r="K67" s="0"/>
       <c r="L67" s="0"/>
+      <c r="M67" s="0"/>
+      <c r="N67" s="0"/>
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
@@ -2005,6 +2156,8 @@
       <c r="J68" s="0"/>
       <c r="K68" s="0"/>
       <c r="L68" s="0"/>
+      <c r="M68" s="0"/>
+      <c r="N68" s="0"/>
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
@@ -2023,6 +2176,8 @@
       <c r="J69" s="0"/>
       <c r="K69" s="0"/>
       <c r="L69" s="0"/>
+      <c r="M69" s="0"/>
+      <c r="N69" s="0"/>
     </row>
     <row r="70">
       <c r="A70" s="0"/>
@@ -2037,6 +2192,8 @@
       <c r="J70" s="0"/>
       <c r="K70" s="0"/>
       <c r="L70" s="0"/>
+      <c r="M70" s="0"/>
+      <c r="N70" s="0"/>
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
@@ -2055,6 +2212,8 @@
       <c r="J71" s="0"/>
       <c r="K71" s="0"/>
       <c r="L71" s="0"/>
+      <c r="M71" s="0"/>
+      <c r="N71" s="0"/>
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
@@ -2073,13 +2232,15 @@
       <c r="J72" s="0"/>
       <c r="K72" s="0"/>
       <c r="L72" s="0"/>
+      <c r="M72" s="0"/>
+      <c r="N72" s="0"/>
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
         <v>24</v>
       </c>
       <c r="B73" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" s="0"/>
       <c r="D73" s="0"/>
@@ -2091,6 +2252,8 @@
       <c r="J73" s="0"/>
       <c r="K73" s="0"/>
       <c r="L73" s="0"/>
+      <c r="M73" s="0"/>
+      <c r="N73" s="0"/>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
@@ -2103,7 +2266,7 @@
         <v>63</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E74" s="0"/>
       <c r="F74" s="0"/>
@@ -2113,6 +2276,8 @@
       <c r="J74" s="0"/>
       <c r="K74" s="0"/>
       <c r="L74" s="0"/>
+      <c r="M74" s="0"/>
+      <c r="N74" s="0"/>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
@@ -2125,7 +2290,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E75" s="0"/>
       <c r="F75" s="0"/>
@@ -2135,6 +2300,8 @@
       <c r="J75" s="0"/>
       <c r="K75" s="0"/>
       <c r="L75" s="0"/>
+      <c r="M75" s="0"/>
+      <c r="N75" s="0"/>
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
@@ -2151,6 +2318,8 @@
       <c r="J76" s="0"/>
       <c r="K76" s="0"/>
       <c r="L76" s="0"/>
+      <c r="M76" s="0"/>
+      <c r="N76" s="0"/>
     </row>
     <row r="77">
       <c r="A77" s="0"/>
@@ -2165,6 +2334,8 @@
       <c r="J77" s="0"/>
       <c r="K77" s="0"/>
       <c r="L77" s="0"/>
+      <c r="M77" s="0"/>
+      <c r="N77" s="0"/>
     </row>
     <row r="78">
       <c r="A78" s="0"/>
@@ -2179,6 +2350,8 @@
       <c r="J78" s="0"/>
       <c r="K78" s="0"/>
       <c r="L78" s="0"/>
+      <c r="M78" s="0"/>
+      <c r="N78" s="0"/>
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
@@ -2195,6 +2368,8 @@
       <c r="J79" s="0"/>
       <c r="K79" s="0"/>
       <c r="L79" s="0"/>
+      <c r="M79" s="0"/>
+      <c r="N79" s="0"/>
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
@@ -2213,6 +2388,8 @@
       <c r="J80" s="0"/>
       <c r="K80" s="0"/>
       <c r="L80" s="0"/>
+      <c r="M80" s="0"/>
+      <c r="N80" s="0"/>
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
@@ -2231,6 +2408,8 @@
       <c r="J81" s="0"/>
       <c r="K81" s="0"/>
       <c r="L81" s="0"/>
+      <c r="M81" s="0"/>
+      <c r="N81" s="0"/>
     </row>
     <row r="82">
       <c r="A82" s="0"/>
@@ -2245,6 +2424,8 @@
       <c r="J82" s="0"/>
       <c r="K82" s="0"/>
       <c r="L82" s="0"/>
+      <c r="M82" s="0"/>
+      <c r="N82" s="0"/>
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
@@ -2263,6 +2444,8 @@
       <c r="J83" s="0"/>
       <c r="K83" s="0"/>
       <c r="L83" s="0"/>
+      <c r="M83" s="0"/>
+      <c r="N83" s="0"/>
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
@@ -2281,6 +2464,8 @@
       <c r="J84" s="0"/>
       <c r="K84" s="0"/>
       <c r="L84" s="0"/>
+      <c r="M84" s="0"/>
+      <c r="N84" s="0"/>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
@@ -2299,6 +2484,8 @@
       <c r="J85" s="0"/>
       <c r="K85" s="0"/>
       <c r="L85" s="0"/>
+      <c r="M85" s="0"/>
+      <c r="N85" s="0"/>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
@@ -2311,7 +2498,7 @@
         <v>61</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E86" s="0"/>
       <c r="F86" s="0"/>
@@ -2321,6 +2508,8 @@
       <c r="J86" s="0"/>
       <c r="K86" s="0"/>
       <c r="L86" s="0"/>
+      <c r="M86" s="0"/>
+      <c r="N86" s="0"/>
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
@@ -2333,7 +2522,7 @@
         <v>1</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E87" s="0"/>
       <c r="F87" s="0"/>
@@ -2343,6 +2532,8 @@
       <c r="J87" s="0"/>
       <c r="K87" s="0"/>
       <c r="L87" s="0"/>
+      <c r="M87" s="0"/>
+      <c r="N87" s="0"/>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
@@ -2359,6 +2550,8 @@
       <c r="J88" s="0"/>
       <c r="K88" s="0"/>
       <c r="L88" s="0"/>
+      <c r="M88" s="0"/>
+      <c r="N88" s="0"/>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
@@ -2375,6 +2568,8 @@
       <c r="J89" s="0"/>
       <c r="K89" s="0"/>
       <c r="L89" s="0"/>
+      <c r="M89" s="0"/>
+      <c r="N89" s="0"/>
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
@@ -2391,6 +2586,8 @@
       <c r="J90" s="0"/>
       <c r="K90" s="0"/>
       <c r="L90" s="0"/>
+      <c r="M90" s="0"/>
+      <c r="N90" s="0"/>
     </row>
     <row r="91">
       <c r="A91" s="0"/>
@@ -2405,6 +2602,8 @@
       <c r="J91" s="0"/>
       <c r="K91" s="0"/>
       <c r="L91" s="0"/>
+      <c r="M91" s="0"/>
+      <c r="N91" s="0"/>
     </row>
     <row r="92">
       <c r="A92" s="0"/>
@@ -2419,6 +2618,8 @@
       <c r="J92" s="0"/>
       <c r="K92" s="0"/>
       <c r="L92" s="0"/>
+      <c r="M92" s="0"/>
+      <c r="N92" s="0"/>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
@@ -2435,6 +2636,8 @@
       <c r="J93" s="0"/>
       <c r="K93" s="0"/>
       <c r="L93" s="0"/>
+      <c r="M93" s="0"/>
+      <c r="N93" s="0"/>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
@@ -2453,6 +2656,8 @@
       <c r="J94" s="0"/>
       <c r="K94" s="0"/>
       <c r="L94" s="0"/>
+      <c r="M94" s="0"/>
+      <c r="N94" s="0"/>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
@@ -2471,6 +2676,8 @@
       <c r="J95" s="0"/>
       <c r="K95" s="0"/>
       <c r="L95" s="0"/>
+      <c r="M95" s="0"/>
+      <c r="N95" s="0"/>
     </row>
     <row r="96">
       <c r="A96" s="0"/>
@@ -2485,6 +2692,8 @@
       <c r="J96" s="0"/>
       <c r="K96" s="0"/>
       <c r="L96" s="0"/>
+      <c r="M96" s="0"/>
+      <c r="N96" s="0"/>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
@@ -2503,6 +2712,8 @@
       <c r="J97" s="0"/>
       <c r="K97" s="0"/>
       <c r="L97" s="0"/>
+      <c r="M97" s="0"/>
+      <c r="N97" s="0"/>
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
@@ -2521,13 +2732,15 @@
       <c r="J98" s="0"/>
       <c r="K98" s="0"/>
       <c r="L98" s="0"/>
+      <c r="M98" s="0"/>
+      <c r="N98" s="0"/>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
         <v>24</v>
       </c>
       <c r="B99" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99" s="0"/>
       <c r="D99" s="0"/>
@@ -2539,6 +2752,8 @@
       <c r="J99" s="0"/>
       <c r="K99" s="0"/>
       <c r="L99" s="0"/>
+      <c r="M99" s="0"/>
+      <c r="N99" s="0"/>
     </row>
     <row r="100">
       <c r="A100" s="0" t="s">
@@ -2551,7 +2766,7 @@
         <v>63</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E100" s="0"/>
       <c r="F100" s="0"/>
@@ -2561,6 +2776,8 @@
       <c r="J100" s="0"/>
       <c r="K100" s="0"/>
       <c r="L100" s="0"/>
+      <c r="M100" s="0"/>
+      <c r="N100" s="0"/>
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
@@ -2573,7 +2790,7 @@
         <v>1</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E101" s="0"/>
       <c r="F101" s="0"/>
@@ -2583,6 +2800,8 @@
       <c r="J101" s="0"/>
       <c r="K101" s="0"/>
       <c r="L101" s="0"/>
+      <c r="M101" s="0"/>
+      <c r="N101" s="0"/>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
@@ -2599,6 +2818,8 @@
       <c r="J102" s="0"/>
       <c r="K102" s="0"/>
       <c r="L102" s="0"/>
+      <c r="M102" s="0"/>
+      <c r="N102" s="0"/>
     </row>
     <row r="103">
       <c r="A103" s="0"/>
@@ -2613,6 +2834,8 @@
       <c r="J103" s="0"/>
       <c r="K103" s="0"/>
       <c r="L103" s="0"/>
+      <c r="M103" s="0"/>
+      <c r="N103" s="0"/>
     </row>
     <row r="104">
       <c r="A104" s="0"/>
@@ -2627,6 +2850,8 @@
       <c r="J104" s="0"/>
       <c r="K104" s="0"/>
       <c r="L104" s="0"/>
+      <c r="M104" s="0"/>
+      <c r="N104" s="0"/>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
@@ -2643,6 +2868,8 @@
       <c r="J105" s="0"/>
       <c r="K105" s="0"/>
       <c r="L105" s="0"/>
+      <c r="M105" s="0"/>
+      <c r="N105" s="0"/>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
@@ -2661,6 +2888,8 @@
       <c r="J106" s="0"/>
       <c r="K106" s="0"/>
       <c r="L106" s="0"/>
+      <c r="M106" s="0"/>
+      <c r="N106" s="0"/>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
@@ -2679,6 +2908,8 @@
       <c r="J107" s="0"/>
       <c r="K107" s="0"/>
       <c r="L107" s="0"/>
+      <c r="M107" s="0"/>
+      <c r="N107" s="0"/>
     </row>
     <row r="108">
       <c r="A108" s="0"/>
@@ -2693,6 +2924,8 @@
       <c r="J108" s="0"/>
       <c r="K108" s="0"/>
       <c r="L108" s="0"/>
+      <c r="M108" s="0"/>
+      <c r="N108" s="0"/>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
@@ -2711,6 +2944,8 @@
       <c r="J109" s="0"/>
       <c r="K109" s="0"/>
       <c r="L109" s="0"/>
+      <c r="M109" s="0"/>
+      <c r="N109" s="0"/>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
@@ -2729,6 +2964,8 @@
       <c r="J110" s="0"/>
       <c r="K110" s="0"/>
       <c r="L110" s="0"/>
+      <c r="M110" s="0"/>
+      <c r="N110" s="0"/>
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
@@ -2747,6 +2984,8 @@
       <c r="J111" s="0"/>
       <c r="K111" s="0"/>
       <c r="L111" s="0"/>
+      <c r="M111" s="0"/>
+      <c r="N111" s="0"/>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
@@ -2759,7 +2998,7 @@
         <v>61</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E112" s="0"/>
       <c r="F112" s="0"/>
@@ -2769,6 +3008,8 @@
       <c r="J112" s="0"/>
       <c r="K112" s="0"/>
       <c r="L112" s="0"/>
+      <c r="M112" s="0"/>
+      <c r="N112" s="0"/>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
@@ -2781,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E113" s="0"/>
       <c r="F113" s="0"/>
@@ -2791,6 +3032,8 @@
       <c r="J113" s="0"/>
       <c r="K113" s="0"/>
       <c r="L113" s="0"/>
+      <c r="M113" s="0"/>
+      <c r="N113" s="0"/>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
@@ -2807,6 +3050,8 @@
       <c r="J114" s="0"/>
       <c r="K114" s="0"/>
       <c r="L114" s="0"/>
+      <c r="M114" s="0"/>
+      <c r="N114" s="0"/>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
@@ -2823,6 +3068,8 @@
       <c r="J115" s="0"/>
       <c r="K115" s="0"/>
       <c r="L115" s="0"/>
+      <c r="M115" s="0"/>
+      <c r="N115" s="0"/>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
@@ -2839,6 +3086,8 @@
       <c r="J116" s="0"/>
       <c r="K116" s="0"/>
       <c r="L116" s="0"/>
+      <c r="M116" s="0"/>
+      <c r="N116" s="0"/>
     </row>
     <row r="117">
       <c r="A117" s="0"/>
@@ -2853,6 +3102,8 @@
       <c r="J117" s="0"/>
       <c r="K117" s="0"/>
       <c r="L117" s="0"/>
+      <c r="M117" s="0"/>
+      <c r="N117" s="0"/>
     </row>
     <row r="118">
       <c r="A118" s="0"/>
@@ -2867,6 +3118,8 @@
       <c r="J118" s="0"/>
       <c r="K118" s="0"/>
       <c r="L118" s="0"/>
+      <c r="M118" s="0"/>
+      <c r="N118" s="0"/>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
@@ -2883,6 +3136,8 @@
       <c r="J119" s="0"/>
       <c r="K119" s="0"/>
       <c r="L119" s="0"/>
+      <c r="M119" s="0"/>
+      <c r="N119" s="0"/>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
@@ -2901,6 +3156,8 @@
       <c r="J120" s="0"/>
       <c r="K120" s="0"/>
       <c r="L120" s="0"/>
+      <c r="M120" s="0"/>
+      <c r="N120" s="0"/>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
@@ -2919,6 +3176,8 @@
       <c r="J121" s="0"/>
       <c r="K121" s="0"/>
       <c r="L121" s="0"/>
+      <c r="M121" s="0"/>
+      <c r="N121" s="0"/>
     </row>
     <row r="122">
       <c r="A122" s="0"/>
@@ -2933,6 +3192,8 @@
       <c r="J122" s="0"/>
       <c r="K122" s="0"/>
       <c r="L122" s="0"/>
+      <c r="M122" s="0"/>
+      <c r="N122" s="0"/>
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
@@ -2951,6 +3212,8 @@
       <c r="J123" s="0"/>
       <c r="K123" s="0"/>
       <c r="L123" s="0"/>
+      <c r="M123" s="0"/>
+      <c r="N123" s="0"/>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
@@ -2969,13 +3232,15 @@
       <c r="J124" s="0"/>
       <c r="K124" s="0"/>
       <c r="L124" s="0"/>
+      <c r="M124" s="0"/>
+      <c r="N124" s="0"/>
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
         <v>24</v>
       </c>
       <c r="B125" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125" s="0"/>
       <c r="D125" s="0"/>
@@ -2987,6 +3252,8 @@
       <c r="J125" s="0"/>
       <c r="K125" s="0"/>
       <c r="L125" s="0"/>
+      <c r="M125" s="0"/>
+      <c r="N125" s="0"/>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
@@ -2999,7 +3266,7 @@
         <v>63</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E126" s="0"/>
       <c r="F126" s="0"/>
@@ -3009,6 +3276,8 @@
       <c r="J126" s="0"/>
       <c r="K126" s="0"/>
       <c r="L126" s="0"/>
+      <c r="M126" s="0"/>
+      <c r="N126" s="0"/>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
@@ -3021,7 +3290,7 @@
         <v>1</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E127" s="0"/>
       <c r="F127" s="0"/>
@@ -3031,6 +3300,8 @@
       <c r="J127" s="0"/>
       <c r="K127" s="0"/>
       <c r="L127" s="0"/>
+      <c r="M127" s="0"/>
+      <c r="N127" s="0"/>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
@@ -3047,6 +3318,8 @@
       <c r="J128" s="0"/>
       <c r="K128" s="0"/>
       <c r="L128" s="0"/>
+      <c r="M128" s="0"/>
+      <c r="N128" s="0"/>
     </row>
     <row r="129">
       <c r="A129" s="0"/>
@@ -3061,6 +3334,8 @@
       <c r="J129" s="0"/>
       <c r="K129" s="0"/>
       <c r="L129" s="0"/>
+      <c r="M129" s="0"/>
+      <c r="N129" s="0"/>
     </row>
     <row r="130">
       <c r="A130" s="0"/>
@@ -3075,6 +3350,8 @@
       <c r="J130" s="0"/>
       <c r="K130" s="0"/>
       <c r="L130" s="0"/>
+      <c r="M130" s="0"/>
+      <c r="N130" s="0"/>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
@@ -3091,6 +3368,8 @@
       <c r="J131" s="0"/>
       <c r="K131" s="0"/>
       <c r="L131" s="0"/>
+      <c r="M131" s="0"/>
+      <c r="N131" s="0"/>
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
@@ -3109,6 +3388,8 @@
       <c r="J132" s="0"/>
       <c r="K132" s="0"/>
       <c r="L132" s="0"/>
+      <c r="M132" s="0"/>
+      <c r="N132" s="0"/>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
@@ -3127,6 +3408,8 @@
       <c r="J133" s="0"/>
       <c r="K133" s="0"/>
       <c r="L133" s="0"/>
+      <c r="M133" s="0"/>
+      <c r="N133" s="0"/>
     </row>
     <row r="134">
       <c r="A134" s="0"/>
@@ -3141,6 +3424,8 @@
       <c r="J134" s="0"/>
       <c r="K134" s="0"/>
       <c r="L134" s="0"/>
+      <c r="M134" s="0"/>
+      <c r="N134" s="0"/>
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
@@ -3159,6 +3444,8 @@
       <c r="J135" s="0"/>
       <c r="K135" s="0"/>
       <c r="L135" s="0"/>
+      <c r="M135" s="0"/>
+      <c r="N135" s="0"/>
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
@@ -3177,6 +3464,8 @@
       <c r="J136" s="0"/>
       <c r="K136" s="0"/>
       <c r="L136" s="0"/>
+      <c r="M136" s="0"/>
+      <c r="N136" s="0"/>
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
@@ -3195,6 +3484,8 @@
       <c r="J137" s="0"/>
       <c r="K137" s="0"/>
       <c r="L137" s="0"/>
+      <c r="M137" s="0"/>
+      <c r="N137" s="0"/>
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
@@ -3207,7 +3498,7 @@
         <v>61</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E138" s="0"/>
       <c r="F138" s="0"/>
@@ -3217,6 +3508,8 @@
       <c r="J138" s="0"/>
       <c r="K138" s="0"/>
       <c r="L138" s="0"/>
+      <c r="M138" s="0"/>
+      <c r="N138" s="0"/>
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
@@ -3229,7 +3522,7 @@
         <v>1</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E139" s="0"/>
       <c r="F139" s="0"/>
@@ -3239,6 +3532,8 @@
       <c r="J139" s="0"/>
       <c r="K139" s="0"/>
       <c r="L139" s="0"/>
+      <c r="M139" s="0"/>
+      <c r="N139" s="0"/>
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
@@ -3255,6 +3550,8 @@
       <c r="J140" s="0"/>
       <c r="K140" s="0"/>
       <c r="L140" s="0"/>
+      <c r="M140" s="0"/>
+      <c r="N140" s="0"/>
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
@@ -3271,6 +3568,8 @@
       <c r="J141" s="0"/>
       <c r="K141" s="0"/>
       <c r="L141" s="0"/>
+      <c r="M141" s="0"/>
+      <c r="N141" s="0"/>
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
@@ -3287,6 +3586,8 @@
       <c r="J142" s="0"/>
       <c r="K142" s="0"/>
       <c r="L142" s="0"/>
+      <c r="M142" s="0"/>
+      <c r="N142" s="0"/>
     </row>
     <row r="143">
       <c r="A143" s="0"/>
@@ -3301,6 +3602,8 @@
       <c r="J143" s="0"/>
       <c r="K143" s="0"/>
       <c r="L143" s="0"/>
+      <c r="M143" s="0"/>
+      <c r="N143" s="0"/>
     </row>
     <row r="144">
       <c r="A144" s="0"/>
@@ -3315,6 +3618,8 @@
       <c r="J144" s="0"/>
       <c r="K144" s="0"/>
       <c r="L144" s="0"/>
+      <c r="M144" s="0"/>
+      <c r="N144" s="0"/>
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
@@ -3331,6 +3636,8 @@
       <c r="J145" s="0"/>
       <c r="K145" s="0"/>
       <c r="L145" s="0"/>
+      <c r="M145" s="0"/>
+      <c r="N145" s="0"/>
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
@@ -3349,6 +3656,8 @@
       <c r="J146" s="0"/>
       <c r="K146" s="0"/>
       <c r="L146" s="0"/>
+      <c r="M146" s="0"/>
+      <c r="N146" s="0"/>
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
@@ -3367,6 +3676,8 @@
       <c r="J147" s="0"/>
       <c r="K147" s="0"/>
       <c r="L147" s="0"/>
+      <c r="M147" s="0"/>
+      <c r="N147" s="0"/>
     </row>
     <row r="148">
       <c r="A148" s="0"/>
@@ -3381,6 +3692,8 @@
       <c r="J148" s="0"/>
       <c r="K148" s="0"/>
       <c r="L148" s="0"/>
+      <c r="M148" s="0"/>
+      <c r="N148" s="0"/>
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
@@ -3399,6 +3712,8 @@
       <c r="J149" s="0"/>
       <c r="K149" s="0"/>
       <c r="L149" s="0"/>
+      <c r="M149" s="0"/>
+      <c r="N149" s="0"/>
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
@@ -3417,13 +3732,15 @@
       <c r="J150" s="0"/>
       <c r="K150" s="0"/>
       <c r="L150" s="0"/>
+      <c r="M150" s="0"/>
+      <c r="N150" s="0"/>
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
         <v>24</v>
       </c>
       <c r="B151" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C151" s="0"/>
       <c r="D151" s="0"/>
@@ -3435,6 +3752,8 @@
       <c r="J151" s="0"/>
       <c r="K151" s="0"/>
       <c r="L151" s="0"/>
+      <c r="M151" s="0"/>
+      <c r="N151" s="0"/>
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
@@ -3447,7 +3766,7 @@
         <v>63</v>
       </c>
       <c r="D152" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E152" s="0"/>
       <c r="F152" s="0"/>
@@ -3457,6 +3776,8 @@
       <c r="J152" s="0"/>
       <c r="K152" s="0"/>
       <c r="L152" s="0"/>
+      <c r="M152" s="0"/>
+      <c r="N152" s="0"/>
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
@@ -3469,7 +3790,7 @@
         <v>1</v>
       </c>
       <c r="D153" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E153" s="0"/>
       <c r="F153" s="0"/>
@@ -3479,6 +3800,8 @@
       <c r="J153" s="0"/>
       <c r="K153" s="0"/>
       <c r="L153" s="0"/>
+      <c r="M153" s="0"/>
+      <c r="N153" s="0"/>
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
@@ -3495,6 +3818,8 @@
       <c r="J154" s="0"/>
       <c r="K154" s="0"/>
       <c r="L154" s="0"/>
+      <c r="M154" s="0"/>
+      <c r="N154" s="0"/>
     </row>
     <row r="155">
       <c r="A155" s="0"/>
@@ -3509,6 +3834,8 @@
       <c r="J155" s="0"/>
       <c r="K155" s="0"/>
       <c r="L155" s="0"/>
+      <c r="M155" s="0"/>
+      <c r="N155" s="0"/>
     </row>
     <row r="156">
       <c r="A156" s="0"/>
@@ -3523,6 +3850,8 @@
       <c r="J156" s="0"/>
       <c r="K156" s="0"/>
       <c r="L156" s="0"/>
+      <c r="M156" s="0"/>
+      <c r="N156" s="0"/>
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
@@ -3539,10 +3868,12 @@
       <c r="J157" s="0"/>
       <c r="K157" s="0"/>
       <c r="L157" s="0"/>
+      <c r="M157" s="0"/>
+      <c r="N157" s="0"/>
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="B158" s="0" t="s">
         <v>133</v>
@@ -3557,13 +3888,15 @@
       <c r="J158" s="0"/>
       <c r="K158" s="0"/>
       <c r="L158" s="0"/>
+      <c r="M158" s="0"/>
+      <c r="N158" s="0"/>
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="B159" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C159" s="0"/>
       <c r="D159" s="0"/>
@@ -3575,14 +3908,12 @@
       <c r="J159" s="0"/>
       <c r="K159" s="0"/>
       <c r="L159" s="0"/>
+      <c r="M159" s="0"/>
+      <c r="N159" s="0"/>
     </row>
     <row r="160">
-      <c r="A160" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="B160" s="0" t="s">
-        <v>143</v>
-      </c>
+      <c r="A160" s="0"/>
+      <c r="B160" s="0"/>
       <c r="C160" s="0"/>
       <c r="D160" s="0"/>
       <c r="E160" s="0"/>
@@ -3593,13 +3924,15 @@
       <c r="J160" s="0"/>
       <c r="K160" s="0"/>
       <c r="L160" s="0"/>
+      <c r="M160" s="0"/>
+      <c r="N160" s="0"/>
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="B161" s="0" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C161" s="0"/>
       <c r="D161" s="0"/>
@@ -3611,68 +3944,62 @@
       <c r="J161" s="0"/>
       <c r="K161" s="0"/>
       <c r="L161" s="0"/>
+      <c r="M161" s="0"/>
+      <c r="N161" s="0"/>
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B162" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="C162" s="0">
-        <v>1958</v>
-      </c>
-      <c r="D162" s="0">
-        <v>8</v>
-      </c>
-      <c r="E162" s="0">
-        <v>29</v>
-      </c>
-      <c r="F162" s="0" t="s">
-        <v>147</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="C162" s="0"/>
+      <c r="D162" s="0"/>
+      <c r="E162" s="0"/>
+      <c r="F162" s="0"/>
       <c r="G162" s="0"/>
       <c r="H162" s="0"/>
       <c r="I162" s="0"/>
       <c r="J162" s="0"/>
       <c r="K162" s="0"/>
       <c r="L162" s="0"/>
+      <c r="M162" s="0"/>
+      <c r="N162" s="0"/>
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B163" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="C163" s="0">
-        <v>1959</v>
-      </c>
-      <c r="D163" s="0">
-        <v>9</v>
-      </c>
-      <c r="E163" s="0">
-        <v>2</v>
-      </c>
-      <c r="F163" s="0" t="s">
-        <v>147</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C163" s="0"/>
+      <c r="D163" s="0"/>
+      <c r="E163" s="0"/>
+      <c r="F163" s="0"/>
       <c r="G163" s="0"/>
       <c r="H163" s="0"/>
       <c r="I163" s="0"/>
       <c r="J163" s="0"/>
       <c r="K163" s="0"/>
       <c r="L163" s="0"/>
+      <c r="M163" s="0"/>
+      <c r="N163" s="0"/>
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="B164" s="0">
-        <v>1</v>
-      </c>
-      <c r="C164" s="0"/>
-      <c r="D164" s="0"/>
+        <v>27</v>
+      </c>
+      <c r="B164" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C164" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="D164" s="0" t="s">
+        <v>148</v>
+      </c>
       <c r="E164" s="0"/>
       <c r="F164" s="0"/>
       <c r="G164" s="0"/>
@@ -3681,16 +4008,22 @@
       <c r="J164" s="0"/>
       <c r="K164" s="0"/>
       <c r="L164" s="0"/>
+      <c r="M164" s="0"/>
+      <c r="N164" s="0"/>
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="B165" s="0">
+        <v>28</v>
+      </c>
+      <c r="B165" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C165" s="0">
         <v>1</v>
       </c>
-      <c r="C165" s="0"/>
-      <c r="D165" s="0"/>
+      <c r="D165" s="0" t="s">
+        <v>148</v>
+      </c>
       <c r="E165" s="0"/>
       <c r="F165" s="0"/>
       <c r="G165" s="0"/>
@@ -3699,14 +4032,14 @@
       <c r="J165" s="0"/>
       <c r="K165" s="0"/>
       <c r="L165" s="0"/>
+      <c r="M165" s="0"/>
+      <c r="N165" s="0"/>
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="B166" s="0">
-        <v>0</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B166" s="0"/>
       <c r="C166" s="0"/>
       <c r="D166" s="0"/>
       <c r="E166" s="0"/>
@@ -3717,14 +4050,14 @@
       <c r="J166" s="0"/>
       <c r="K166" s="0"/>
       <c r="L166" s="0"/>
+      <c r="M166" s="0"/>
+      <c r="N166" s="0"/>
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="B167" s="0">
-        <v>2</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B167" s="0"/>
       <c r="C167" s="0"/>
       <c r="D167" s="0"/>
       <c r="E167" s="0"/>
@@ -3735,20 +4068,16 @@
       <c r="J167" s="0"/>
       <c r="K167" s="0"/>
       <c r="L167" s="0"/>
+      <c r="M167" s="0"/>
+      <c r="N167" s="0"/>
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="B168" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="C168" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="D168" s="0" t="s">
-        <v>147</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B168" s="0"/>
+      <c r="C168" s="0"/>
+      <c r="D168" s="0"/>
       <c r="E168" s="0"/>
       <c r="F168" s="0"/>
       <c r="G168" s="0"/>
@@ -3757,20 +4086,14 @@
       <c r="J168" s="0"/>
       <c r="K168" s="0"/>
       <c r="L168" s="0"/>
+      <c r="M168" s="0"/>
+      <c r="N168" s="0"/>
     </row>
     <row r="169">
-      <c r="A169" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="B169" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="C169" s="0">
-        <v>1</v>
-      </c>
-      <c r="D169" s="0" t="s">
-        <v>147</v>
-      </c>
+      <c r="A169" s="0"/>
+      <c r="B169" s="0"/>
+      <c r="C169" s="0"/>
+      <c r="D169" s="0"/>
       <c r="E169" s="0"/>
       <c r="F169" s="0"/>
       <c r="G169" s="0"/>
@@ -3779,11 +4102,11 @@
       <c r="J169" s="0"/>
       <c r="K169" s="0"/>
       <c r="L169" s="0"/>
+      <c r="M169" s="0"/>
+      <c r="N169" s="0"/>
     </row>
     <row r="170">
-      <c r="A170" s="0" t="s">
-        <v>8</v>
-      </c>
+      <c r="A170" s="0"/>
       <c r="B170" s="0"/>
       <c r="C170" s="0"/>
       <c r="D170" s="0"/>
@@ -3795,9 +4118,13 @@
       <c r="J170" s="0"/>
       <c r="K170" s="0"/>
       <c r="L170" s="0"/>
+      <c r="M170" s="0"/>
+      <c r="N170" s="0"/>
     </row>
     <row r="171">
-      <c r="A171" s="0"/>
+      <c r="A171" s="0" t="s">
+        <v>0</v>
+      </c>
       <c r="B171" s="0"/>
       <c r="C171" s="0"/>
       <c r="D171" s="0"/>
@@ -3809,10 +4136,12 @@
       <c r="J171" s="0"/>
       <c r="K171" s="0"/>
       <c r="L171" s="0"/>
+      <c r="M171" s="0"/>
+      <c r="N171" s="0"/>
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="B172" s="0" t="s">
         <v>133</v>
@@ -3827,13 +4156,15 @@
       <c r="J172" s="0"/>
       <c r="K172" s="0"/>
       <c r="L172" s="0"/>
+      <c r="M172" s="0"/>
+      <c r="N172" s="0"/>
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="B173" s="0">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C173" s="0"/>
       <c r="D173" s="0"/>
@@ -3845,14 +4176,12 @@
       <c r="J173" s="0"/>
       <c r="K173" s="0"/>
       <c r="L173" s="0"/>
+      <c r="M173" s="0"/>
+      <c r="N173" s="0"/>
     </row>
     <row r="174">
-      <c r="A174" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="B174" s="0">
-        <v>0.20000000000000001</v>
-      </c>
+      <c r="A174" s="0"/>
+      <c r="B174" s="0"/>
       <c r="C174" s="0"/>
       <c r="D174" s="0"/>
       <c r="E174" s="0"/>
@@ -3863,12 +4192,16 @@
       <c r="J174" s="0"/>
       <c r="K174" s="0"/>
       <c r="L174" s="0"/>
+      <c r="M174" s="0"/>
+      <c r="N174" s="0"/>
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B175" s="0"/>
+        <v>21</v>
+      </c>
+      <c r="B175" s="0" t="s">
+        <v>139</v>
+      </c>
       <c r="C175" s="0"/>
       <c r="D175" s="0"/>
       <c r="E175" s="0"/>
@@ -3879,10 +4212,16 @@
       <c r="J175" s="0"/>
       <c r="K175" s="0"/>
       <c r="L175" s="0"/>
+      <c r="M175" s="0"/>
+      <c r="N175" s="0"/>
     </row>
     <row r="176">
-      <c r="A176" s="0"/>
-      <c r="B176" s="0"/>
+      <c r="A176" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B176" s="0" t="s">
+        <v>46</v>
+      </c>
       <c r="C176" s="0"/>
       <c r="D176" s="0"/>
       <c r="E176" s="0"/>
@@ -3893,10 +4232,16 @@
       <c r="J176" s="0"/>
       <c r="K176" s="0"/>
       <c r="L176" s="0"/>
+      <c r="M176" s="0"/>
+      <c r="N176" s="0"/>
     </row>
     <row r="177">
-      <c r="A177" s="0"/>
-      <c r="B177" s="0"/>
+      <c r="A177" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B177" s="0">
+        <v>2</v>
+      </c>
       <c r="C177" s="0"/>
       <c r="D177" s="0"/>
       <c r="E177" s="0"/>
@@ -3907,14 +4252,22 @@
       <c r="J177" s="0"/>
       <c r="K177" s="0"/>
       <c r="L177" s="0"/>
+      <c r="M177" s="0"/>
+      <c r="N177" s="0"/>
     </row>
     <row r="178">
       <c r="A178" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B178" s="0"/>
-      <c r="C178" s="0"/>
-      <c r="D178" s="0"/>
+        <v>27</v>
+      </c>
+      <c r="B178" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C178" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="D178" s="0" t="s">
+        <v>148</v>
+      </c>
       <c r="E178" s="0"/>
       <c r="F178" s="0"/>
       <c r="G178" s="0"/>
@@ -3923,16 +4276,22 @@
       <c r="J178" s="0"/>
       <c r="K178" s="0"/>
       <c r="L178" s="0"/>
+      <c r="M178" s="0"/>
+      <c r="N178" s="0"/>
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="C179" s="0"/>
-      <c r="D179" s="0"/>
+        <v>134</v>
+      </c>
+      <c r="C179" s="0">
+        <v>1</v>
+      </c>
+      <c r="D179" s="0" t="s">
+        <v>148</v>
+      </c>
       <c r="E179" s="0"/>
       <c r="F179" s="0"/>
       <c r="G179" s="0"/>
@@ -3941,14 +4300,14 @@
       <c r="J179" s="0"/>
       <c r="K179" s="0"/>
       <c r="L179" s="0"/>
+      <c r="M179" s="0"/>
+      <c r="N179" s="0"/>
     </row>
     <row r="180">
       <c r="A180" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="B180" s="0">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B180" s="0"/>
       <c r="C180" s="0"/>
       <c r="D180" s="0"/>
       <c r="E180" s="0"/>
@@ -3959,13 +4318,13 @@
       <c r="J180" s="0"/>
       <c r="K180" s="0"/>
       <c r="L180" s="0"/>
+      <c r="M180" s="0"/>
+      <c r="N180" s="0"/>
     </row>
     <row r="181">
       <c r="A181" s="0"/>
       <c r="B181" s="0"/>
-      <c r="C181" s="0" t="s">
-        <v>155</v>
-      </c>
+      <c r="C181" s="0"/>
       <c r="D181" s="0"/>
       <c r="E181" s="0"/>
       <c r="F181" s="0"/>
@@ -3975,20 +4334,14 @@
       <c r="J181" s="0"/>
       <c r="K181" s="0"/>
       <c r="L181" s="0"/>
+      <c r="M181" s="0"/>
+      <c r="N181" s="0"/>
     </row>
     <row r="182">
-      <c r="A182" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="B182" s="0">
-        <v>5</v>
-      </c>
-      <c r="C182" s="0">
-        <v>5</v>
-      </c>
-      <c r="D182" s="0" t="s">
-        <v>161</v>
-      </c>
+      <c r="A182" s="0"/>
+      <c r="B182" s="0"/>
+      <c r="C182" s="0"/>
+      <c r="D182" s="0"/>
       <c r="E182" s="0"/>
       <c r="F182" s="0"/>
       <c r="G182" s="0"/>
@@ -3997,10 +4350,12 @@
       <c r="J182" s="0"/>
       <c r="K182" s="0"/>
       <c r="L182" s="0"/>
+      <c r="M182" s="0"/>
+      <c r="N182" s="0"/>
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B183" s="0"/>
       <c r="C183" s="0"/>
@@ -4013,10 +4368,16 @@
       <c r="J183" s="0"/>
       <c r="K183" s="0"/>
       <c r="L183" s="0"/>
+      <c r="M183" s="0"/>
+      <c r="N183" s="0"/>
     </row>
     <row r="184">
-      <c r="A184" s="0"/>
-      <c r="B184" s="0"/>
+      <c r="A184" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B184" s="0" t="s">
+        <v>133</v>
+      </c>
       <c r="C184" s="0"/>
       <c r="D184" s="0"/>
       <c r="E184" s="0"/>
@@ -4027,10 +4388,16 @@
       <c r="J184" s="0"/>
       <c r="K184" s="0"/>
       <c r="L184" s="0"/>
+      <c r="M184" s="0"/>
+      <c r="N184" s="0"/>
     </row>
     <row r="185">
-      <c r="A185" s="0"/>
-      <c r="B185" s="0"/>
+      <c r="A185" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B185" s="0">
+        <v>1</v>
+      </c>
       <c r="C185" s="0"/>
       <c r="D185" s="0"/>
       <c r="E185" s="0"/>
@@ -4041,12 +4408,16 @@
       <c r="J185" s="0"/>
       <c r="K185" s="0"/>
       <c r="L185" s="0"/>
+      <c r="M185" s="0"/>
+      <c r="N185" s="0"/>
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B186" s="0"/>
+        <v>47</v>
+      </c>
+      <c r="B186" s="0" t="s">
+        <v>144</v>
+      </c>
       <c r="C186" s="0"/>
       <c r="D186" s="0"/>
       <c r="E186" s="0"/>
@@ -4057,13 +4428,15 @@
       <c r="J186" s="0"/>
       <c r="K186" s="0"/>
       <c r="L186" s="0"/>
+      <c r="M186" s="0"/>
+      <c r="N186" s="0"/>
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C187" s="0"/>
       <c r="D187" s="0"/>
@@ -4075,48 +4448,74 @@
       <c r="J187" s="0"/>
       <c r="K187" s="0"/>
       <c r="L187" s="0"/>
+      <c r="M187" s="0"/>
+      <c r="N187" s="0"/>
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="B188" s="0">
-        <v>1</v>
-      </c>
-      <c r="C188" s="0"/>
-      <c r="D188" s="0"/>
-      <c r="E188" s="0"/>
-      <c r="F188" s="0"/>
+        <v>49</v>
+      </c>
+      <c r="B188" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C188" s="0">
+        <v>1958</v>
+      </c>
+      <c r="D188" s="0">
+        <v>8</v>
+      </c>
+      <c r="E188" s="0">
+        <v>29</v>
+      </c>
+      <c r="F188" s="0" t="s">
+        <v>148</v>
+      </c>
       <c r="G188" s="0"/>
       <c r="H188" s="0"/>
       <c r="I188" s="0"/>
       <c r="J188" s="0"/>
       <c r="K188" s="0"/>
       <c r="L188" s="0"/>
+      <c r="M188" s="0"/>
+      <c r="N188" s="0"/>
     </row>
     <row r="189">
-      <c r="A189" s="0"/>
-      <c r="B189" s="0"/>
-      <c r="C189" s="0"/>
-      <c r="D189" s="0"/>
-      <c r="E189" s="0"/>
-      <c r="F189" s="0"/>
+      <c r="A189" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="B189" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C189" s="0">
+        <v>1958</v>
+      </c>
+      <c r="D189" s="0">
+        <v>8</v>
+      </c>
+      <c r="E189" s="0">
+        <v>30</v>
+      </c>
+      <c r="F189" s="0" t="s">
+        <v>148</v>
+      </c>
       <c r="G189" s="0"/>
       <c r="H189" s="0"/>
       <c r="I189" s="0"/>
       <c r="J189" s="0"/>
       <c r="K189" s="0"/>
       <c r="L189" s="0"/>
+      <c r="M189" s="0"/>
+      <c r="N189" s="0"/>
     </row>
     <row r="190">
       <c r="A190" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="B190" s="0"/>
+        <v>51</v>
+      </c>
+      <c r="B190" s="0">
+        <v>1</v>
+      </c>
       <c r="C190" s="0"/>
-      <c r="D190" s="0" t="s">
-        <v>162</v>
-      </c>
+      <c r="D190" s="0"/>
       <c r="E190" s="0"/>
       <c r="F190" s="0"/>
       <c r="G190" s="0"/>
@@ -4125,12 +4524,16 @@
       <c r="J190" s="0"/>
       <c r="K190" s="0"/>
       <c r="L190" s="0"/>
+      <c r="M190" s="0"/>
+      <c r="N190" s="0"/>
     </row>
     <row r="191">
       <c r="A191" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="B191" s="0"/>
+        <v>52</v>
+      </c>
+      <c r="B191" s="0">
+        <v>1</v>
+      </c>
       <c r="C191" s="0"/>
       <c r="D191" s="0"/>
       <c r="E191" s="0"/>
@@ -4141,18 +4544,18 @@
       <c r="J191" s="0"/>
       <c r="K191" s="0"/>
       <c r="L191" s="0"/>
+      <c r="M191" s="0"/>
+      <c r="N191" s="0"/>
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="B192" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C192" s="0"/>
-      <c r="D192" s="0" t="s">
-        <v>163</v>
-      </c>
+      <c r="D192" s="0"/>
       <c r="E192" s="0"/>
       <c r="F192" s="0"/>
       <c r="G192" s="0"/>
@@ -4161,20 +4564,18 @@
       <c r="J192" s="0"/>
       <c r="K192" s="0"/>
       <c r="L192" s="0"/>
+      <c r="M192" s="0"/>
+      <c r="N192" s="0"/>
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="B193" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="C193" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="D193" s="0" t="s">
-        <v>164</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B193" s="0">
+        <v>2</v>
+      </c>
+      <c r="C193" s="0"/>
+      <c r="D193" s="0"/>
       <c r="E193" s="0"/>
       <c r="F193" s="0"/>
       <c r="G193" s="0"/>
@@ -4183,19 +4584,21 @@
       <c r="J193" s="0"/>
       <c r="K193" s="0"/>
       <c r="L193" s="0"/>
+      <c r="M193" s="0"/>
+      <c r="N193" s="0"/>
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="B194" s="0">
-        <v>1</v>
-      </c>
-      <c r="C194" s="0">
-        <v>1</v>
+        <v>55</v>
+      </c>
+      <c r="B194" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C194" s="0" t="s">
+        <v>58</v>
       </c>
       <c r="D194" s="0" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="E194" s="0"/>
       <c r="F194" s="0"/>
@@ -4205,14 +4608,22 @@
       <c r="J194" s="0"/>
       <c r="K194" s="0"/>
       <c r="L194" s="0"/>
+      <c r="M194" s="0"/>
+      <c r="N194" s="0"/>
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B195" s="0"/>
-      <c r="C195" s="0"/>
-      <c r="D195" s="0"/>
+        <v>56</v>
+      </c>
+      <c r="B195" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C195" s="0">
+        <v>1</v>
+      </c>
+      <c r="D195" s="0" t="s">
+        <v>148</v>
+      </c>
       <c r="E195" s="0"/>
       <c r="F195" s="0"/>
       <c r="G195" s="0"/>
@@ -4221,9 +4632,13 @@
       <c r="J195" s="0"/>
       <c r="K195" s="0"/>
       <c r="L195" s="0"/>
+      <c r="M195" s="0"/>
+      <c r="N195" s="0"/>
     </row>
     <row r="196">
-      <c r="A196" s="0"/>
+      <c r="A196" s="0" t="s">
+        <v>8</v>
+      </c>
       <c r="B196" s="0"/>
       <c r="C196" s="0"/>
       <c r="D196" s="0"/>
@@ -4235,6 +4650,8 @@
       <c r="J196" s="0"/>
       <c r="K196" s="0"/>
       <c r="L196" s="0"/>
+      <c r="M196" s="0"/>
+      <c r="N196" s="0"/>
     </row>
     <row r="197">
       <c r="A197" s="0"/>
@@ -4249,12 +4666,16 @@
       <c r="J197" s="0"/>
       <c r="K197" s="0"/>
       <c r="L197" s="0"/>
+      <c r="M197" s="0"/>
+      <c r="N197" s="0"/>
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B198" s="0"/>
+        <v>57</v>
+      </c>
+      <c r="B198" s="0" t="s">
+        <v>133</v>
+      </c>
       <c r="C198" s="0"/>
       <c r="D198" s="0"/>
       <c r="E198" s="0"/>
@@ -4265,13 +4686,15 @@
       <c r="J198" s="0"/>
       <c r="K198" s="0"/>
       <c r="L198" s="0"/>
+      <c r="M198" s="0"/>
+      <c r="N198" s="0"/>
     </row>
     <row r="199">
       <c r="A199" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="B199" s="0" t="s">
-        <v>133</v>
+        <v>58</v>
+      </c>
+      <c r="B199" s="0">
+        <v>1</v>
       </c>
       <c r="C199" s="0"/>
       <c r="D199" s="0"/>
@@ -4283,13 +4706,15 @@
       <c r="J199" s="0"/>
       <c r="K199" s="0"/>
       <c r="L199" s="0"/>
+      <c r="M199" s="0"/>
+      <c r="N199" s="0"/>
     </row>
     <row r="200">
       <c r="A200" s="0" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B200" s="0">
-        <v>1</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="C200" s="0"/>
       <c r="D200" s="0"/>
@@ -4301,9 +4726,13 @@
       <c r="J200" s="0"/>
       <c r="K200" s="0"/>
       <c r="L200" s="0"/>
+      <c r="M200" s="0"/>
+      <c r="N200" s="0"/>
     </row>
     <row r="201">
-      <c r="A201" s="0"/>
+      <c r="A201" s="0" t="s">
+        <v>8</v>
+      </c>
       <c r="B201" s="0"/>
       <c r="C201" s="0"/>
       <c r="D201" s="0"/>
@@ -4315,45 +4744,31 @@
       <c r="J201" s="0"/>
       <c r="K201" s="0"/>
       <c r="L201" s="0"/>
+      <c r="M201" s="0"/>
+      <c r="N201" s="0"/>
     </row>
     <row r="202">
-      <c r="A202" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="B202" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="C202" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="D202" s="0" t="s">
-        <v>166</v>
-      </c>
-      <c r="E202" s="0" t="s">
-        <v>211</v>
-      </c>
-      <c r="F202" s="0" t="s">
-        <v>147</v>
-      </c>
+      <c r="A202" s="0"/>
+      <c r="B202" s="0"/>
+      <c r="C202" s="0"/>
+      <c r="D202" s="0"/>
+      <c r="E202" s="0"/>
+      <c r="F202" s="0"/>
       <c r="G202" s="0"/>
       <c r="H202" s="0"/>
       <c r="I202" s="0"/>
       <c r="J202" s="0"/>
       <c r="K202" s="0"/>
       <c r="L202" s="0"/>
+      <c r="M202" s="0"/>
+      <c r="N202" s="0"/>
     </row>
     <row r="203">
       <c r="A203" s="0"/>
       <c r="B203" s="0"/>
-      <c r="C203" s="0">
-        <v>0</v>
-      </c>
-      <c r="D203" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="E203" s="0">
-        <v>0.5</v>
-      </c>
+      <c r="C203" s="0"/>
+      <c r="D203" s="0"/>
+      <c r="E203" s="0"/>
       <c r="F203" s="0"/>
       <c r="G203" s="0"/>
       <c r="H203" s="0"/>
@@ -4361,19 +4776,17 @@
       <c r="J203" s="0"/>
       <c r="K203" s="0"/>
       <c r="L203" s="0"/>
+      <c r="M203" s="0"/>
+      <c r="N203" s="0"/>
     </row>
     <row r="204">
-      <c r="A204" s="0"/>
+      <c r="A204" s="0" t="s">
+        <v>0</v>
+      </c>
       <c r="B204" s="0"/>
-      <c r="C204" s="0">
-        <v>0.5</v>
-      </c>
-      <c r="D204" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="E204" s="0">
-        <v>3</v>
-      </c>
+      <c r="C204" s="0"/>
+      <c r="D204" s="0"/>
+      <c r="E204" s="0"/>
       <c r="F204" s="0"/>
       <c r="G204" s="0"/>
       <c r="H204" s="0"/>
@@ -4381,19 +4794,19 @@
       <c r="J204" s="0"/>
       <c r="K204" s="0"/>
       <c r="L204" s="0"/>
+      <c r="M204" s="0"/>
+      <c r="N204" s="0"/>
     </row>
     <row r="205">
-      <c r="A205" s="0"/>
-      <c r="B205" s="0"/>
-      <c r="C205" s="0">
-        <v>3</v>
-      </c>
-      <c r="D205" s="0">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="E205" s="0">
-        <v>10</v>
-      </c>
+      <c r="A205" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B205" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="C205" s="0"/>
+      <c r="D205" s="0"/>
+      <c r="E205" s="0"/>
       <c r="F205" s="0"/>
       <c r="G205" s="0"/>
       <c r="H205" s="0"/>
@@ -4401,19 +4814,19 @@
       <c r="J205" s="0"/>
       <c r="K205" s="0"/>
       <c r="L205" s="0"/>
+      <c r="M205" s="0"/>
+      <c r="N205" s="0"/>
     </row>
     <row r="206">
-      <c r="A206" s="0"/>
-      <c r="B206" s="0"/>
-      <c r="C206" s="0">
-        <v>10</v>
-      </c>
-      <c r="D206" s="0">
-        <v>1</v>
-      </c>
-      <c r="E206" s="0">
-        <v>50</v>
-      </c>
+      <c r="A206" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B206" s="0">
+        <v>2</v>
+      </c>
+      <c r="C206" s="0"/>
+      <c r="D206" s="0"/>
+      <c r="E206" s="0"/>
       <c r="F206" s="0"/>
       <c r="G206" s="0"/>
       <c r="H206" s="0"/>
@@ -4421,19 +4834,19 @@
       <c r="J206" s="0"/>
       <c r="K206" s="0"/>
       <c r="L206" s="0"/>
+      <c r="M206" s="0"/>
+      <c r="N206" s="0"/>
     </row>
     <row r="207">
-      <c r="A207" s="0"/>
-      <c r="B207" s="0"/>
-      <c r="C207" s="0">
-        <v>50</v>
-      </c>
-      <c r="D207" s="0">
-        <v>5</v>
-      </c>
-      <c r="E207" s="0">
-        <v>100</v>
-      </c>
+      <c r="A207" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B207" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="C207" s="0"/>
+      <c r="D207" s="0"/>
+      <c r="E207" s="0"/>
       <c r="F207" s="0"/>
       <c r="G207" s="0"/>
       <c r="H207" s="0"/>
@@ -4441,11 +4854,15 @@
       <c r="J207" s="0"/>
       <c r="K207" s="0"/>
       <c r="L207" s="0"/>
+      <c r="M207" s="0"/>
+      <c r="N207" s="0"/>
     </row>
     <row r="208">
-      <c r="A208" s="0"/>
+      <c r="A208" s="0" t="s">
+        <v>48</v>
+      </c>
       <c r="B208" s="0" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C208" s="0"/>
       <c r="D208" s="0"/>
@@ -4457,40 +4874,72 @@
       <c r="J208" s="0"/>
       <c r="K208" s="0"/>
       <c r="L208" s="0"/>
+      <c r="M208" s="0"/>
+      <c r="N208" s="0"/>
     </row>
     <row r="209">
       <c r="A209" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B209" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C209" s="0">
+        <v>1958</v>
+      </c>
+      <c r="D209" s="0">
         <v>8</v>
       </c>
-      <c r="B209" s="0"/>
-      <c r="C209" s="0"/>
-      <c r="D209" s="0"/>
-      <c r="E209" s="0"/>
-      <c r="F209" s="0"/>
+      <c r="E209" s="0">
+        <v>29</v>
+      </c>
+      <c r="F209" s="0" t="s">
+        <v>148</v>
+      </c>
       <c r="G209" s="0"/>
       <c r="H209" s="0"/>
       <c r="I209" s="0"/>
       <c r="J209" s="0"/>
       <c r="K209" s="0"/>
       <c r="L209" s="0"/>
+      <c r="M209" s="0"/>
+      <c r="N209" s="0"/>
     </row>
     <row r="210">
-      <c r="A210" s="0"/>
-      <c r="B210" s="0"/>
-      <c r="C210" s="0"/>
-      <c r="D210" s="0"/>
-      <c r="E210" s="0"/>
-      <c r="F210" s="0"/>
+      <c r="A210" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="B210" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C210" s="0">
+        <v>1959</v>
+      </c>
+      <c r="D210" s="0">
+        <v>9</v>
+      </c>
+      <c r="E210" s="0">
+        <v>2</v>
+      </c>
+      <c r="F210" s="0" t="s">
+        <v>148</v>
+      </c>
       <c r="G210" s="0"/>
       <c r="H210" s="0"/>
       <c r="I210" s="0"/>
       <c r="J210" s="0"/>
       <c r="K210" s="0"/>
       <c r="L210" s="0"/>
+      <c r="M210" s="0"/>
+      <c r="N210" s="0"/>
     </row>
     <row r="211">
-      <c r="A211" s="0"/>
-      <c r="B211" s="0"/>
+      <c r="A211" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="B211" s="0">
+        <v>1</v>
+      </c>
       <c r="C211" s="0"/>
       <c r="D211" s="0"/>
       <c r="E211" s="0"/>
@@ -4501,12 +4950,16 @@
       <c r="J211" s="0"/>
       <c r="K211" s="0"/>
       <c r="L211" s="0"/>
+      <c r="M211" s="0"/>
+      <c r="N211" s="0"/>
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B212" s="0"/>
+        <v>52</v>
+      </c>
+      <c r="B212" s="0">
+        <v>1</v>
+      </c>
       <c r="C212" s="0"/>
       <c r="D212" s="0"/>
       <c r="E212" s="0"/>
@@ -4517,13 +4970,15 @@
       <c r="J212" s="0"/>
       <c r="K212" s="0"/>
       <c r="L212" s="0"/>
+      <c r="M212" s="0"/>
+      <c r="N212" s="0"/>
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="B213" s="0" t="s">
-        <v>133</v>
+        <v>53</v>
+      </c>
+      <c r="B213" s="0">
+        <v>0</v>
       </c>
       <c r="C213" s="0"/>
       <c r="D213" s="0"/>
@@ -4535,13 +4990,15 @@
       <c r="J213" s="0"/>
       <c r="K213" s="0"/>
       <c r="L213" s="0"/>
+      <c r="M213" s="0"/>
+      <c r="N213" s="0"/>
     </row>
     <row r="214">
       <c r="A214" s="0" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="B214" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C214" s="0"/>
       <c r="D214" s="0"/>
@@ -4553,12 +5010,22 @@
       <c r="J214" s="0"/>
       <c r="K214" s="0"/>
       <c r="L214" s="0"/>
+      <c r="M214" s="0"/>
+      <c r="N214" s="0"/>
     </row>
     <row r="215">
-      <c r="A215" s="0"/>
-      <c r="B215" s="0"/>
-      <c r="C215" s="0"/>
-      <c r="D215" s="0"/>
+      <c r="A215" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B215" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C215" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="D215" s="0" t="s">
+        <v>148</v>
+      </c>
       <c r="E215" s="0"/>
       <c r="F215" s="0"/>
       <c r="G215" s="0"/>
@@ -4567,44 +5034,40 @@
       <c r="J215" s="0"/>
       <c r="K215" s="0"/>
       <c r="L215" s="0"/>
+      <c r="M215" s="0"/>
+      <c r="N215" s="0"/>
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="B216" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C216" s="0">
+        <v>1</v>
+      </c>
+      <c r="D216" s="0" t="s">
         <v>148</v>
       </c>
-      <c r="C216" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="D216" s="0" t="s">
-        <v>167</v>
-      </c>
-      <c r="E216" s="0" t="s">
-        <v>147</v>
-      </c>
-      <c r="F216" s="0" t="s">
-        <v>214</v>
-      </c>
+      <c r="E216" s="0"/>
+      <c r="F216" s="0"/>
       <c r="G216" s="0"/>
       <c r="H216" s="0"/>
       <c r="I216" s="0"/>
       <c r="J216" s="0"/>
       <c r="K216" s="0"/>
       <c r="L216" s="0"/>
+      <c r="M216" s="0"/>
+      <c r="N216" s="0"/>
     </row>
     <row r="217">
-      <c r="A217" s="0"/>
-      <c r="B217" s="0">
-        <v>0</v>
-      </c>
-      <c r="C217" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D217" s="0">
-        <v>1</v>
-      </c>
+      <c r="A217" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B217" s="0"/>
+      <c r="C217" s="0"/>
+      <c r="D217" s="0"/>
       <c r="E217" s="0"/>
       <c r="F217" s="0"/>
       <c r="G217" s="0"/>
@@ -4613,33 +5076,31 @@
       <c r="J217" s="0"/>
       <c r="K217" s="0"/>
       <c r="L217" s="0"/>
+      <c r="M217" s="0"/>
+      <c r="N217" s="0"/>
     </row>
     <row r="218">
       <c r="A218" s="0"/>
-      <c r="B218" s="0">
-        <v>5</v>
-      </c>
-      <c r="C218" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="D218" s="0">
-        <v>1</v>
-      </c>
+      <c r="B218" s="0"/>
+      <c r="C218" s="0"/>
+      <c r="D218" s="0"/>
       <c r="E218" s="0"/>
-      <c r="F218" s="0" t="s">
-        <v>215</v>
-      </c>
+      <c r="F218" s="0"/>
       <c r="G218" s="0"/>
       <c r="H218" s="0"/>
       <c r="I218" s="0"/>
       <c r="J218" s="0"/>
       <c r="K218" s="0"/>
       <c r="L218" s="0"/>
+      <c r="M218" s="0"/>
+      <c r="N218" s="0"/>
     </row>
     <row r="219">
-      <c r="A219" s="0"/>
+      <c r="A219" s="0" t="s">
+        <v>57</v>
+      </c>
       <c r="B219" s="0" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="C219" s="0"/>
       <c r="D219" s="0"/>
@@ -4651,18 +5112,18 @@
       <c r="J219" s="0"/>
       <c r="K219" s="0"/>
       <c r="L219" s="0"/>
+      <c r="M219" s="0"/>
+      <c r="N219" s="0"/>
     </row>
     <row r="220">
       <c r="A220" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="B220" s="0" t="s">
-        <v>105</v>
+        <v>58</v>
+      </c>
+      <c r="B220" s="0">
+        <v>1</v>
       </c>
       <c r="C220" s="0"/>
-      <c r="D220" s="0" t="s">
-        <v>168</v>
-      </c>
+      <c r="D220" s="0"/>
       <c r="E220" s="0"/>
       <c r="F220" s="0"/>
       <c r="G220" s="0"/>
@@ -4671,13 +5132,15 @@
       <c r="J220" s="0"/>
       <c r="K220" s="0"/>
       <c r="L220" s="0"/>
+      <c r="M220" s="0"/>
+      <c r="N220" s="0"/>
     </row>
     <row r="221">
       <c r="A221" s="0" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B221" s="0">
-        <v>1</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="C221" s="0"/>
       <c r="D221" s="0"/>
@@ -4689,20 +5152,16 @@
       <c r="J221" s="0"/>
       <c r="K221" s="0"/>
       <c r="L221" s="0"/>
+      <c r="M221" s="0"/>
+      <c r="N221" s="0"/>
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="B222" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="C222" s="0" t="s">
-        <v>147</v>
-      </c>
-      <c r="D222" s="0" t="s">
-        <v>169</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B222" s="0"/>
+      <c r="C222" s="0"/>
+      <c r="D222" s="0"/>
       <c r="E222" s="0"/>
       <c r="F222" s="0"/>
       <c r="G222" s="0"/>
@@ -4711,17 +5170,13 @@
       <c r="J222" s="0"/>
       <c r="K222" s="0"/>
       <c r="L222" s="0"/>
+      <c r="M222" s="0"/>
+      <c r="N222" s="0"/>
     </row>
     <row r="223">
-      <c r="A223" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="B223" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="C223" s="0" t="s">
-        <v>147</v>
-      </c>
+      <c r="A223" s="0"/>
+      <c r="B223" s="0"/>
+      <c r="C223" s="0"/>
       <c r="D223" s="0"/>
       <c r="E223" s="0"/>
       <c r="F223" s="0"/>
@@ -4731,11 +5186,11 @@
       <c r="J223" s="0"/>
       <c r="K223" s="0"/>
       <c r="L223" s="0"/>
+      <c r="M223" s="0"/>
+      <c r="N223" s="0"/>
     </row>
     <row r="224">
-      <c r="A224" s="0" t="s">
-        <v>8</v>
-      </c>
+      <c r="A224" s="0"/>
       <c r="B224" s="0"/>
       <c r="C224" s="0"/>
       <c r="D224" s="0"/>
@@ -4747,9 +5202,13 @@
       <c r="J224" s="0"/>
       <c r="K224" s="0"/>
       <c r="L224" s="0"/>
+      <c r="M224" s="0"/>
+      <c r="N224" s="0"/>
     </row>
     <row r="225">
-      <c r="A225" s="0"/>
+      <c r="A225" s="0" t="s">
+        <v>0</v>
+      </c>
       <c r="B225" s="0"/>
       <c r="C225" s="0"/>
       <c r="D225" s="0"/>
@@ -4761,10 +5220,16 @@
       <c r="J225" s="0"/>
       <c r="K225" s="0"/>
       <c r="L225" s="0"/>
+      <c r="M225" s="0"/>
+      <c r="N225" s="0"/>
     </row>
     <row r="226">
-      <c r="A226" s="0"/>
-      <c r="B226" s="0"/>
+      <c r="A226" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="B226" s="0" t="s">
+        <v>133</v>
+      </c>
       <c r="C226" s="0"/>
       <c r="D226" s="0"/>
       <c r="E226" s="0"/>
@@ -4775,12 +5240,16 @@
       <c r="J226" s="0"/>
       <c r="K226" s="0"/>
       <c r="L226" s="0"/>
+      <c r="M226" s="0"/>
+      <c r="N226" s="0"/>
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B227" s="0"/>
+        <v>61</v>
+      </c>
+      <c r="B227" s="0">
+        <v>1</v>
+      </c>
       <c r="C227" s="0"/>
       <c r="D227" s="0"/>
       <c r="E227" s="0"/>
@@ -4791,18 +5260,16 @@
       <c r="J227" s="0"/>
       <c r="K227" s="0"/>
       <c r="L227" s="0"/>
+      <c r="M227" s="0"/>
+      <c r="N227" s="0"/>
     </row>
     <row r="228">
-      <c r="A228" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="B228" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="C228" s="0"/>
-      <c r="D228" s="0" t="s">
-        <v>170</v>
-      </c>
+      <c r="A228" s="0"/>
+      <c r="B228" s="0"/>
+      <c r="C228" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="D228" s="0"/>
       <c r="E228" s="0"/>
       <c r="F228" s="0"/>
       <c r="G228" s="0"/>
@@ -4811,17 +5278,21 @@
       <c r="J228" s="0"/>
       <c r="K228" s="0"/>
       <c r="L228" s="0"/>
+      <c r="M228" s="0"/>
+      <c r="N228" s="0"/>
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="B229" s="0">
-        <v>1</v>
-      </c>
-      <c r="C229" s="0"/>
+        <v>5</v>
+      </c>
+      <c r="C229" s="0">
+        <v>5</v>
+      </c>
       <c r="D229" s="0" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="E229" s="0"/>
       <c r="F229" s="0"/>
@@ -4831,9 +5302,13 @@
       <c r="J229" s="0"/>
       <c r="K229" s="0"/>
       <c r="L229" s="0"/>
+      <c r="M229" s="0"/>
+      <c r="N229" s="0"/>
     </row>
     <row r="230">
-      <c r="A230" s="0"/>
+      <c r="A230" s="0" t="s">
+        <v>8</v>
+      </c>
       <c r="B230" s="0"/>
       <c r="C230" s="0"/>
       <c r="D230" s="0"/>
@@ -4845,179 +5320,139 @@
       <c r="J230" s="0"/>
       <c r="K230" s="0"/>
       <c r="L230" s="0"/>
+      <c r="M230" s="0"/>
+      <c r="N230" s="0"/>
     </row>
     <row r="231">
-      <c r="A231" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="B231" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="C231" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="D231" s="0" t="s">
-        <v>172</v>
-      </c>
-      <c r="E231" s="0" t="s">
-        <v>212</v>
-      </c>
-      <c r="F231" s="0" t="s">
-        <v>216</v>
-      </c>
-      <c r="G231" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="H231" s="0" t="s">
-        <v>220</v>
-      </c>
-      <c r="I231" s="0" t="s">
-        <v>147</v>
-      </c>
-      <c r="J231" s="0" t="s">
-        <v>221</v>
-      </c>
+      <c r="A231" s="0"/>
+      <c r="B231" s="0"/>
+      <c r="C231" s="0"/>
+      <c r="D231" s="0"/>
+      <c r="E231" s="0"/>
+      <c r="F231" s="0"/>
+      <c r="G231" s="0"/>
+      <c r="H231" s="0"/>
+      <c r="I231" s="0"/>
+      <c r="J231" s="0"/>
       <c r="K231" s="0"/>
       <c r="L231" s="0"/>
+      <c r="M231" s="0"/>
+      <c r="N231" s="0"/>
     </row>
     <row r="232">
       <c r="A232" s="0"/>
-      <c r="B232" s="0">
-        <v>0</v>
-      </c>
-      <c r="C232" s="0">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="D232" s="0">
-        <v>0.59999999999999998</v>
-      </c>
-      <c r="E232" s="0">
-        <v>0</v>
-      </c>
-      <c r="F232" s="0">
-        <v>2</v>
-      </c>
-      <c r="G232" s="0">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="H232" s="0">
-        <v>9.9999999999999996e-07</v>
-      </c>
+      <c r="B232" s="0"/>
+      <c r="C232" s="0"/>
+      <c r="D232" s="0"/>
+      <c r="E232" s="0"/>
+      <c r="F232" s="0"/>
+      <c r="G232" s="0"/>
+      <c r="H232" s="0"/>
       <c r="I232" s="0"/>
       <c r="J232" s="0"/>
       <c r="K232" s="0"/>
       <c r="L232" s="0"/>
+      <c r="M232" s="0"/>
+      <c r="N232" s="0"/>
     </row>
     <row r="233">
-      <c r="A233" s="0"/>
-      <c r="B233" s="0">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="C233" s="0">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="D233" s="0">
-        <v>0.59999999999999998</v>
-      </c>
-      <c r="E233" s="0">
+      <c r="A233" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="F233" s="0">
-        <v>2</v>
-      </c>
-      <c r="G233" s="0">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="H233" s="0">
-        <v>9.9999999999999996e-07</v>
-      </c>
+      <c r="B233" s="0"/>
+      <c r="C233" s="0"/>
+      <c r="D233" s="0"/>
+      <c r="E233" s="0"/>
+      <c r="F233" s="0"/>
+      <c r="G233" s="0"/>
+      <c r="H233" s="0"/>
       <c r="I233" s="0"/>
       <c r="J233" s="0"/>
       <c r="K233" s="0"/>
       <c r="L233" s="0"/>
+      <c r="M233" s="0"/>
+      <c r="N233" s="0"/>
     </row>
     <row r="234">
-      <c r="A234" s="0"/>
-      <c r="B234" s="0">
-        <v>5</v>
-      </c>
-      <c r="C234" s="0">
-        <v>0.029999999999999999</v>
-      </c>
-      <c r="D234" s="0">
-        <v>0.96999999999999997</v>
-      </c>
-      <c r="E234" s="0">
-        <v>0</v>
-      </c>
-      <c r="F234" s="0">
-        <v>1</v>
-      </c>
-      <c r="G234" s="0">
-        <v>0.029999999999999999</v>
-      </c>
-      <c r="H234" s="0">
-        <v>9.9999999999999996e-07</v>
-      </c>
+      <c r="A234" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="B234" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="C234" s="0"/>
+      <c r="D234" s="0"/>
+      <c r="E234" s="0"/>
+      <c r="F234" s="0"/>
+      <c r="G234" s="0"/>
+      <c r="H234" s="0"/>
       <c r="I234" s="0"/>
       <c r="J234" s="0"/>
       <c r="K234" s="0"/>
       <c r="L234" s="0"/>
+      <c r="M234" s="0"/>
+      <c r="N234" s="0"/>
     </row>
     <row r="235">
-      <c r="A235" s="0"/>
-      <c r="B235" s="0" t="s">
-        <v>147</v>
+      <c r="A235" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B235" s="0">
+        <v>1</v>
       </c>
       <c r="C235" s="0"/>
       <c r="D235" s="0"/>
       <c r="E235" s="0"/>
       <c r="F235" s="0"/>
-      <c r="G235" s="0" t="s">
-        <v>217</v>
-      </c>
+      <c r="G235" s="0"/>
       <c r="H235" s="0"/>
       <c r="I235" s="0"/>
       <c r="J235" s="0"/>
       <c r="K235" s="0"/>
       <c r="L235" s="0"/>
+      <c r="M235" s="0"/>
+      <c r="N235" s="0"/>
     </row>
     <row r="236">
-      <c r="A236" s="0" t="s">
-        <v>8</v>
-      </c>
+      <c r="A236" s="0"/>
       <c r="B236" s="0"/>
       <c r="C236" s="0"/>
       <c r="D236" s="0"/>
       <c r="E236" s="0"/>
       <c r="F236" s="0"/>
-      <c r="G236" s="0" t="s">
-        <v>218</v>
-      </c>
+      <c r="G236" s="0"/>
       <c r="H236" s="0"/>
       <c r="I236" s="0"/>
       <c r="J236" s="0"/>
       <c r="K236" s="0"/>
       <c r="L236" s="0"/>
+      <c r="M236" s="0"/>
+      <c r="N236" s="0"/>
     </row>
     <row r="237">
-      <c r="A237" s="0"/>
+      <c r="A237" s="0" t="s">
+        <v>64</v>
+      </c>
       <c r="B237" s="0"/>
       <c r="C237" s="0"/>
-      <c r="D237" s="0"/>
+      <c r="D237" s="0" t="s">
+        <v>163</v>
+      </c>
       <c r="E237" s="0"/>
       <c r="F237" s="0"/>
-      <c r="G237" s="0" t="s">
-        <v>219</v>
-      </c>
+      <c r="G237" s="0"/>
       <c r="H237" s="0"/>
       <c r="I237" s="0"/>
       <c r="J237" s="0"/>
       <c r="K237" s="0"/>
       <c r="L237" s="0"/>
+      <c r="M237" s="0"/>
+      <c r="N237" s="0"/>
     </row>
     <row r="238">
-      <c r="A238" s="0"/>
+      <c r="A238" s="0" t="s">
+        <v>65</v>
+      </c>
       <c r="B238" s="0"/>
       <c r="C238" s="0"/>
       <c r="D238" s="0"/>
@@ -5029,12 +5464,20 @@
       <c r="J238" s="0"/>
       <c r="K238" s="0"/>
       <c r="L238" s="0"/>
+      <c r="M238" s="0"/>
+      <c r="N238" s="0"/>
     </row>
     <row r="239">
-      <c r="A239" s="0"/>
-      <c r="B239" s="0"/>
+      <c r="A239" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B239" s="0">
+        <v>1</v>
+      </c>
       <c r="C239" s="0"/>
-      <c r="D239" s="0"/>
+      <c r="D239" s="0" t="s">
+        <v>164</v>
+      </c>
       <c r="E239" s="0"/>
       <c r="F239" s="0"/>
       <c r="G239" s="0"/>
@@ -5043,14 +5486,22 @@
       <c r="J239" s="0"/>
       <c r="K239" s="0"/>
       <c r="L239" s="0"/>
+      <c r="M239" s="0"/>
+      <c r="N239" s="0"/>
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B240" s="0"/>
-      <c r="C240" s="0"/>
-      <c r="D240" s="0"/>
+        <v>67</v>
+      </c>
+      <c r="B240" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="C240" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="D240" s="0" t="s">
+        <v>165</v>
+      </c>
       <c r="E240" s="0"/>
       <c r="F240" s="0"/>
       <c r="G240" s="0"/>
@@ -5059,16 +5510,22 @@
       <c r="J240" s="0"/>
       <c r="K240" s="0"/>
       <c r="L240" s="0"/>
+      <c r="M240" s="0"/>
+      <c r="N240" s="0"/>
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="B241" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="C241" s="0"/>
-      <c r="D241" s="0"/>
+        <v>68</v>
+      </c>
+      <c r="B241" s="0">
+        <v>1</v>
+      </c>
+      <c r="C241" s="0">
+        <v>1</v>
+      </c>
+      <c r="D241" s="0" t="s">
+        <v>166</v>
+      </c>
       <c r="E241" s="0"/>
       <c r="F241" s="0"/>
       <c r="G241" s="0"/>
@@ -5077,14 +5534,14 @@
       <c r="J241" s="0"/>
       <c r="K241" s="0"/>
       <c r="L241" s="0"/>
+      <c r="M241" s="0"/>
+      <c r="N241" s="0"/>
     </row>
     <row r="242">
       <c r="A242" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="B242" s="0">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B242" s="0"/>
       <c r="C242" s="0"/>
       <c r="D242" s="0"/>
       <c r="E242" s="0"/>
@@ -5095,6 +5552,8 @@
       <c r="J242" s="0"/>
       <c r="K242" s="0"/>
       <c r="L242" s="0"/>
+      <c r="M242" s="0"/>
+      <c r="N242" s="0"/>
     </row>
     <row r="243">
       <c r="A243" s="0"/>
@@ -5109,20 +5568,14 @@
       <c r="J243" s="0"/>
       <c r="K243" s="0"/>
       <c r="L243" s="0"/>
+      <c r="M243" s="0"/>
+      <c r="N243" s="0"/>
     </row>
     <row r="244">
-      <c r="A244" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="B244" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="C244" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="D244" s="0" t="s">
-        <v>147</v>
-      </c>
+      <c r="A244" s="0"/>
+      <c r="B244" s="0"/>
+      <c r="C244" s="0"/>
+      <c r="D244" s="0"/>
       <c r="E244" s="0"/>
       <c r="F244" s="0"/>
       <c r="G244" s="0"/>
@@ -5131,15 +5584,15 @@
       <c r="J244" s="0"/>
       <c r="K244" s="0"/>
       <c r="L244" s="0"/>
+      <c r="M244" s="0"/>
+      <c r="N244" s="0"/>
     </row>
     <row r="245">
-      <c r="A245" s="0"/>
-      <c r="B245" s="0">
+      <c r="A245" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="C245" s="0">
-        <v>-2</v>
-      </c>
+      <c r="B245" s="0"/>
+      <c r="C245" s="0"/>
       <c r="D245" s="0"/>
       <c r="E245" s="0"/>
       <c r="F245" s="0"/>
@@ -5149,15 +5602,17 @@
       <c r="J245" s="0"/>
       <c r="K245" s="0"/>
       <c r="L245" s="0"/>
+      <c r="M245" s="0"/>
+      <c r="N245" s="0"/>
     </row>
     <row r="246">
-      <c r="A246" s="0"/>
-      <c r="B246" s="0">
-        <v>100</v>
-      </c>
-      <c r="C246" s="0">
-        <v>-2</v>
-      </c>
+      <c r="A246" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B246" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="C246" s="0"/>
       <c r="D246" s="0"/>
       <c r="E246" s="0"/>
       <c r="F246" s="0"/>
@@ -5167,11 +5622,15 @@
       <c r="J246" s="0"/>
       <c r="K246" s="0"/>
       <c r="L246" s="0"/>
+      <c r="M246" s="0"/>
+      <c r="N246" s="0"/>
     </row>
     <row r="247">
-      <c r="A247" s="0"/>
-      <c r="B247" s="0" t="s">
-        <v>147</v>
+      <c r="A247" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="B247" s="0">
+        <v>1</v>
       </c>
       <c r="C247" s="0"/>
       <c r="D247" s="0"/>
@@ -5183,11 +5642,11 @@
       <c r="J247" s="0"/>
       <c r="K247" s="0"/>
       <c r="L247" s="0"/>
+      <c r="M247" s="0"/>
+      <c r="N247" s="0"/>
     </row>
     <row r="248">
-      <c r="A248" s="0" t="s">
-        <v>8</v>
-      </c>
+      <c r="A248" s="0"/>
       <c r="B248" s="0"/>
       <c r="C248" s="0"/>
       <c r="D248" s="0"/>
@@ -5199,27 +5658,49 @@
       <c r="J248" s="0"/>
       <c r="K248" s="0"/>
       <c r="L248" s="0"/>
+      <c r="M248" s="0"/>
+      <c r="N248" s="0"/>
     </row>
     <row r="249">
-      <c r="A249" s="0"/>
-      <c r="B249" s="0"/>
-      <c r="C249" s="0"/>
-      <c r="D249" s="0"/>
-      <c r="E249" s="0"/>
-      <c r="F249" s="0"/>
+      <c r="A249" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B249" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="C249" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="D249" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="E249" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="F249" s="0" t="s">
+        <v>148</v>
+      </c>
       <c r="G249" s="0"/>
       <c r="H249" s="0"/>
       <c r="I249" s="0"/>
       <c r="J249" s="0"/>
       <c r="K249" s="0"/>
       <c r="L249" s="0"/>
+      <c r="M249" s="0"/>
+      <c r="N249" s="0"/>
     </row>
     <row r="250">
       <c r="A250" s="0"/>
       <c r="B250" s="0"/>
-      <c r="C250" s="0"/>
-      <c r="D250" s="0"/>
-      <c r="E250" s="0"/>
+      <c r="C250" s="0">
+        <v>0</v>
+      </c>
+      <c r="D250" s="0">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="E250" s="0">
+        <v>0.5</v>
+      </c>
       <c r="F250" s="0"/>
       <c r="G250" s="0"/>
       <c r="H250" s="0"/>
@@ -5227,15 +5708,21 @@
       <c r="J250" s="0"/>
       <c r="K250" s="0"/>
       <c r="L250" s="0"/>
+      <c r="M250" s="0"/>
+      <c r="N250" s="0"/>
     </row>
     <row r="251">
-      <c r="A251" s="0" t="s">
-        <v>0</v>
-      </c>
+      <c r="A251" s="0"/>
       <c r="B251" s="0"/>
-      <c r="C251" s="0"/>
-      <c r="D251" s="0"/>
-      <c r="E251" s="0"/>
+      <c r="C251" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="D251" s="0">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="E251" s="0">
+        <v>3</v>
+      </c>
       <c r="F251" s="0"/>
       <c r="G251" s="0"/>
       <c r="H251" s="0"/>
@@ -5243,17 +5730,21 @@
       <c r="J251" s="0"/>
       <c r="K251" s="0"/>
       <c r="L251" s="0"/>
+      <c r="M251" s="0"/>
+      <c r="N251" s="0"/>
     </row>
     <row r="252">
-      <c r="A252" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="B252" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="C252" s="0"/>
-      <c r="D252" s="0"/>
-      <c r="E252" s="0"/>
+      <c r="A252" s="0"/>
+      <c r="B252" s="0"/>
+      <c r="C252" s="0">
+        <v>3</v>
+      </c>
+      <c r="D252" s="0">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="E252" s="0">
+        <v>10</v>
+      </c>
       <c r="F252" s="0"/>
       <c r="G252" s="0"/>
       <c r="H252" s="0"/>
@@ -5261,17 +5752,21 @@
       <c r="J252" s="0"/>
       <c r="K252" s="0"/>
       <c r="L252" s="0"/>
+      <c r="M252" s="0"/>
+      <c r="N252" s="0"/>
     </row>
     <row r="253">
-      <c r="A253" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="B253" s="0">
+      <c r="A253" s="0"/>
+      <c r="B253" s="0"/>
+      <c r="C253" s="0">
+        <v>10</v>
+      </c>
+      <c r="D253" s="0">
         <v>1</v>
       </c>
-      <c r="C253" s="0"/>
-      <c r="D253" s="0"/>
-      <c r="E253" s="0"/>
+      <c r="E253" s="0">
+        <v>50</v>
+      </c>
       <c r="F253" s="0"/>
       <c r="G253" s="0"/>
       <c r="H253" s="0"/>
@@ -5279,15 +5774,21 @@
       <c r="J253" s="0"/>
       <c r="K253" s="0"/>
       <c r="L253" s="0"/>
+      <c r="M253" s="0"/>
+      <c r="N253" s="0"/>
     </row>
     <row r="254">
       <c r="A254" s="0"/>
       <c r="B254" s="0"/>
-      <c r="C254" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="D254" s="0"/>
-      <c r="E254" s="0"/>
+      <c r="C254" s="0">
+        <v>50</v>
+      </c>
+      <c r="D254" s="0">
+        <v>5</v>
+      </c>
+      <c r="E254" s="0">
+        <v>100</v>
+      </c>
       <c r="F254" s="0"/>
       <c r="G254" s="0"/>
       <c r="H254" s="0"/>
@@ -5295,20 +5796,16 @@
       <c r="J254" s="0"/>
       <c r="K254" s="0"/>
       <c r="L254" s="0"/>
+      <c r="M254" s="0"/>
+      <c r="N254" s="0"/>
     </row>
     <row r="255">
-      <c r="A255" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="B255" s="0">
-        <v>0.25</v>
-      </c>
-      <c r="C255" s="0">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="D255" s="0" t="s">
-        <v>173</v>
-      </c>
+      <c r="A255" s="0"/>
+      <c r="B255" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="C255" s="0"/>
+      <c r="D255" s="0"/>
       <c r="E255" s="0"/>
       <c r="F255" s="0"/>
       <c r="G255" s="0"/>
@@ -5317,20 +5814,16 @@
       <c r="J255" s="0"/>
       <c r="K255" s="0"/>
       <c r="L255" s="0"/>
+      <c r="M255" s="0"/>
+      <c r="N255" s="0"/>
     </row>
     <row r="256">
       <c r="A256" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="B256" s="0">
-        <v>0.98999999999999999</v>
-      </c>
-      <c r="C256" s="0">
-        <v>0.98999999999999999</v>
-      </c>
-      <c r="D256" s="0" t="s">
-        <v>174</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B256" s="0"/>
+      <c r="C256" s="0"/>
+      <c r="D256" s="0"/>
       <c r="E256" s="0"/>
       <c r="F256" s="0"/>
       <c r="G256" s="0"/>
@@ -5339,20 +5832,14 @@
       <c r="J256" s="0"/>
       <c r="K256" s="0"/>
       <c r="L256" s="0"/>
+      <c r="M256" s="0"/>
+      <c r="N256" s="0"/>
     </row>
     <row r="257">
-      <c r="A257" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="B257" s="0">
-        <v>0.27000000000000002</v>
-      </c>
-      <c r="C257" s="0">
-        <v>0.01</v>
-      </c>
-      <c r="D257" s="0" t="s">
-        <v>175</v>
-      </c>
+      <c r="A257" s="0"/>
+      <c r="B257" s="0"/>
+      <c r="C257" s="0"/>
+      <c r="D257" s="0"/>
       <c r="E257" s="0"/>
       <c r="F257" s="0"/>
       <c r="G257" s="0"/>
@@ -5361,20 +5848,14 @@
       <c r="J257" s="0"/>
       <c r="K257" s="0"/>
       <c r="L257" s="0"/>
+      <c r="M257" s="0"/>
+      <c r="N257" s="0"/>
     </row>
     <row r="258">
-      <c r="A258" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="B258" s="0">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="C258" s="0">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="D258" s="0" t="s">
-        <v>176</v>
-      </c>
+      <c r="A258" s="0"/>
+      <c r="B258" s="0"/>
+      <c r="C258" s="0"/>
+      <c r="D258" s="0"/>
       <c r="E258" s="0"/>
       <c r="F258" s="0"/>
       <c r="G258" s="0"/>
@@ -5383,20 +5864,16 @@
       <c r="J258" s="0"/>
       <c r="K258" s="0"/>
       <c r="L258" s="0"/>
+      <c r="M258" s="0"/>
+      <c r="N258" s="0"/>
     </row>
     <row r="259">
       <c r="A259" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="B259" s="0">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="C259" s="0">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="D259" s="0" t="s">
-        <v>177</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B259" s="0"/>
+      <c r="C259" s="0"/>
+      <c r="D259" s="0"/>
       <c r="E259" s="0"/>
       <c r="F259" s="0"/>
       <c r="G259" s="0"/>
@@ -5405,20 +5882,18 @@
       <c r="J259" s="0"/>
       <c r="K259" s="0"/>
       <c r="L259" s="0"/>
+      <c r="M259" s="0"/>
+      <c r="N259" s="0"/>
     </row>
     <row r="260">
       <c r="A260" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="B260" s="0">
-        <v>0.5</v>
-      </c>
-      <c r="C260" s="0">
-        <v>0.5</v>
-      </c>
-      <c r="D260" s="0" t="s">
-        <v>178</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="B260" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="C260" s="0"/>
+      <c r="D260" s="0"/>
       <c r="E260" s="0"/>
       <c r="F260" s="0"/>
       <c r="G260" s="0"/>
@@ -5427,20 +5902,18 @@
       <c r="J260" s="0"/>
       <c r="K260" s="0"/>
       <c r="L260" s="0"/>
+      <c r="M260" s="0"/>
+      <c r="N260" s="0"/>
     </row>
     <row r="261">
       <c r="A261" s="0" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="B261" s="0">
-        <v>1.0000000000000001e-05</v>
-      </c>
-      <c r="C261" s="0">
-        <v>1.0000000000000001e-05</v>
-      </c>
-      <c r="D261" s="0" t="s">
-        <v>179</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C261" s="0"/>
+      <c r="D261" s="0"/>
       <c r="E261" s="0"/>
       <c r="F261" s="0"/>
       <c r="G261" s="0"/>
@@ -5449,20 +5922,14 @@
       <c r="J261" s="0"/>
       <c r="K261" s="0"/>
       <c r="L261" s="0"/>
+      <c r="M261" s="0"/>
+      <c r="N261" s="0"/>
     </row>
     <row r="262">
-      <c r="A262" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="B262" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="C262" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="D262" s="0" t="s">
-        <v>180</v>
-      </c>
+      <c r="A262" s="0"/>
+      <c r="B262" s="0"/>
+      <c r="C262" s="0"/>
+      <c r="D262" s="0"/>
       <c r="E262" s="0"/>
       <c r="F262" s="0"/>
       <c r="G262" s="0"/>
@@ -5471,41 +5938,47 @@
       <c r="J262" s="0"/>
       <c r="K262" s="0"/>
       <c r="L262" s="0"/>
+      <c r="M262" s="0"/>
+      <c r="N262" s="0"/>
     </row>
     <row r="263">
       <c r="A263" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="B263" s="0">
-        <v>3600</v>
-      </c>
-      <c r="C263" s="0">
-        <v>3600</v>
+        <v>74</v>
+      </c>
+      <c r="B263" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C263" s="0" t="s">
+        <v>158</v>
       </c>
       <c r="D263" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="E263" s="0"/>
-      <c r="F263" s="0"/>
+        <v>168</v>
+      </c>
+      <c r="E263" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="F263" s="0" t="s">
+        <v>215</v>
+      </c>
       <c r="G263" s="0"/>
       <c r="H263" s="0"/>
       <c r="I263" s="0"/>
       <c r="J263" s="0"/>
       <c r="K263" s="0"/>
       <c r="L263" s="0"/>
+      <c r="M263" s="0"/>
+      <c r="N263" s="0"/>
     </row>
     <row r="264">
-      <c r="A264" s="0" t="s">
-        <v>95</v>
-      </c>
+      <c r="A264" s="0"/>
       <c r="B264" s="0">
-        <v>50000</v>
-      </c>
-      <c r="C264" s="0">
-        <v>50000</v>
-      </c>
-      <c r="D264" s="0" t="s">
-        <v>182</v>
+        <v>0</v>
+      </c>
+      <c r="C264" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="D264" s="0">
+        <v>1</v>
       </c>
       <c r="E264" s="0"/>
       <c r="F264" s="0"/>
@@ -5515,42 +5988,40 @@
       <c r="J264" s="0"/>
       <c r="K264" s="0"/>
       <c r="L264" s="0"/>
+      <c r="M264" s="0"/>
+      <c r="N264" s="0"/>
     </row>
     <row r="265">
-      <c r="A265" s="0" t="s">
-        <v>96</v>
-      </c>
+      <c r="A265" s="0"/>
       <c r="B265" s="0">
-        <v>1000</v>
-      </c>
-      <c r="C265" s="0">
-        <v>1000</v>
-      </c>
-      <c r="D265" s="0" t="s">
-        <v>183</v>
+        <v>5</v>
+      </c>
+      <c r="C265" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="D265" s="0">
+        <v>1</v>
       </c>
       <c r="E265" s="0"/>
-      <c r="F265" s="0"/>
+      <c r="F265" s="0" t="s">
+        <v>216</v>
+      </c>
       <c r="G265" s="0"/>
       <c r="H265" s="0"/>
       <c r="I265" s="0"/>
       <c r="J265" s="0"/>
       <c r="K265" s="0"/>
       <c r="L265" s="0"/>
+      <c r="M265" s="0"/>
+      <c r="N265" s="0"/>
     </row>
     <row r="266">
-      <c r="A266" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="B266" s="0">
-        <v>1000</v>
-      </c>
-      <c r="C266" s="0">
-        <v>1000</v>
-      </c>
-      <c r="D266" s="0" t="s">
-        <v>184</v>
-      </c>
+      <c r="A266" s="0"/>
+      <c r="B266" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="C266" s="0"/>
+      <c r="D266" s="0"/>
       <c r="E266" s="0"/>
       <c r="F266" s="0"/>
       <c r="G266" s="0"/>
@@ -5559,19 +6030,19 @@
       <c r="J266" s="0"/>
       <c r="K266" s="0"/>
       <c r="L266" s="0"/>
+      <c r="M266" s="0"/>
+      <c r="N266" s="0"/>
     </row>
     <row r="267">
       <c r="A267" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="B267" s="0">
-        <v>-40</v>
-      </c>
-      <c r="C267" s="0">
-        <v>-50</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="B267" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="C267" s="0"/>
       <c r="D267" s="0" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="E267" s="0"/>
       <c r="F267" s="0"/>
@@ -5581,20 +6052,18 @@
       <c r="J267" s="0"/>
       <c r="K267" s="0"/>
       <c r="L267" s="0"/>
+      <c r="M267" s="0"/>
+      <c r="N267" s="0"/>
     </row>
     <row r="268">
       <c r="A268" s="0" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="B268" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="C268" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="D268" s="0" t="s">
-        <v>186</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C268" s="0"/>
+      <c r="D268" s="0"/>
       <c r="E268" s="0"/>
       <c r="F268" s="0"/>
       <c r="G268" s="0"/>
@@ -5603,19 +6072,21 @@
       <c r="J268" s="0"/>
       <c r="K268" s="0"/>
       <c r="L268" s="0"/>
+      <c r="M268" s="0"/>
+      <c r="N268" s="0"/>
     </row>
     <row r="269">
       <c r="A269" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="B269" s="0">
-        <v>0.96999999999999997</v>
-      </c>
-      <c r="C269" s="0">
-        <v>0.96999999999999997</v>
+        <v>77</v>
+      </c>
+      <c r="B269" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C269" s="0" t="s">
+        <v>148</v>
       </c>
       <c r="D269" s="0" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="E269" s="0"/>
       <c r="F269" s="0"/>
@@ -5625,20 +6096,20 @@
       <c r="J269" s="0"/>
       <c r="K269" s="0"/>
       <c r="L269" s="0"/>
+      <c r="M269" s="0"/>
+      <c r="N269" s="0"/>
     </row>
     <row r="270">
       <c r="A270" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="B270" s="0">
-        <v>0.029999999999999999</v>
-      </c>
-      <c r="C270" s="0">
-        <v>0.029999999999999999</v>
-      </c>
-      <c r="D270" s="0" t="s">
-        <v>188</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="B270" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C270" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="D270" s="0"/>
       <c r="E270" s="0"/>
       <c r="F270" s="0"/>
       <c r="G270" s="0"/>
@@ -5647,6 +6118,8 @@
       <c r="J270" s="0"/>
       <c r="K270" s="0"/>
       <c r="L270" s="0"/>
+      <c r="M270" s="0"/>
+      <c r="N270" s="0"/>
     </row>
     <row r="271">
       <c r="A271" s="0" t="s">
@@ -5663,6 +6136,8 @@
       <c r="J271" s="0"/>
       <c r="K271" s="0"/>
       <c r="L271" s="0"/>
+      <c r="M271" s="0"/>
+      <c r="N271" s="0"/>
     </row>
     <row r="272">
       <c r="A272" s="0"/>
@@ -5677,6 +6152,8 @@
       <c r="J272" s="0"/>
       <c r="K272" s="0"/>
       <c r="L272" s="0"/>
+      <c r="M272" s="0"/>
+      <c r="N272" s="0"/>
     </row>
     <row r="273">
       <c r="A273" s="0"/>
@@ -5691,6 +6168,8 @@
       <c r="J273" s="0"/>
       <c r="K273" s="0"/>
       <c r="L273" s="0"/>
+      <c r="M273" s="0"/>
+      <c r="N273" s="0"/>
     </row>
     <row r="274">
       <c r="A274" s="0" t="s">
@@ -5707,16 +6186,20 @@
       <c r="J274" s="0"/>
       <c r="K274" s="0"/>
       <c r="L274" s="0"/>
+      <c r="M274" s="0"/>
+      <c r="N274" s="0"/>
     </row>
     <row r="275">
       <c r="A275" s="0" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B275" s="0" t="s">
         <v>133</v>
       </c>
       <c r="C275" s="0"/>
-      <c r="D275" s="0"/>
+      <c r="D275" s="0" t="s">
+        <v>171</v>
+      </c>
       <c r="E275" s="0"/>
       <c r="F275" s="0"/>
       <c r="G275" s="0"/>
@@ -5725,16 +6208,20 @@
       <c r="J275" s="0"/>
       <c r="K275" s="0"/>
       <c r="L275" s="0"/>
+      <c r="M275" s="0"/>
+      <c r="N275" s="0"/>
     </row>
     <row r="276">
       <c r="A276" s="0" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="B276" s="0">
         <v>1</v>
       </c>
       <c r="C276" s="0"/>
-      <c r="D276" s="0"/>
+      <c r="D276" s="0" t="s">
+        <v>172</v>
+      </c>
       <c r="E276" s="0"/>
       <c r="F276" s="0"/>
       <c r="G276" s="0"/>
@@ -5743,13 +6230,13 @@
       <c r="J276" s="0"/>
       <c r="K276" s="0"/>
       <c r="L276" s="0"/>
+      <c r="M276" s="0"/>
+      <c r="N276" s="0"/>
     </row>
     <row r="277">
       <c r="A277" s="0"/>
       <c r="B277" s="0"/>
-      <c r="C277" s="0" t="s">
-        <v>155</v>
-      </c>
+      <c r="C277" s="0"/>
       <c r="D277" s="0"/>
       <c r="E277" s="0"/>
       <c r="F277" s="0"/>
@@ -5759,165 +6246,195 @@
       <c r="J277" s="0"/>
       <c r="K277" s="0"/>
       <c r="L277" s="0"/>
+      <c r="M277" s="0"/>
+      <c r="N277" s="0"/>
     </row>
     <row r="278">
       <c r="A278" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="B278" s="0">
-        <v>0.25</v>
-      </c>
-      <c r="C278" s="0">
-        <v>0.20000000000000001</v>
+        <v>81</v>
+      </c>
+      <c r="B278" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C278" s="0" t="s">
+        <v>159</v>
       </c>
       <c r="D278" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="E278" s="0"/>
-      <c r="F278" s="0"/>
-      <c r="G278" s="0"/>
-      <c r="H278" s="0"/>
-      <c r="I278" s="0"/>
-      <c r="J278" s="0"/>
+      <c r="E278" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="F278" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="G278" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="H278" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="I278" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="J278" s="0" t="s">
+        <v>222</v>
+      </c>
       <c r="K278" s="0"/>
       <c r="L278" s="0"/>
+      <c r="M278" s="0"/>
+      <c r="N278" s="0"/>
     </row>
     <row r="279">
-      <c r="A279" s="0" t="s">
-        <v>87</v>
-      </c>
+      <c r="A279" s="0"/>
       <c r="B279" s="0">
-        <v>0.98999999999999999</v>
+        <v>0</v>
       </c>
       <c r="C279" s="0">
-        <v>0.98999999999999999</v>
-      </c>
-      <c r="D279" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="E279" s="0"/>
-      <c r="F279" s="0"/>
-      <c r="G279" s="0"/>
-      <c r="H279" s="0"/>
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="D279" s="0">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="E279" s="0">
+        <v>0</v>
+      </c>
+      <c r="F279" s="0">
+        <v>2</v>
+      </c>
+      <c r="G279" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="H279" s="0">
+        <v>9.9999999999999996e-07</v>
+      </c>
       <c r="I279" s="0"/>
       <c r="J279" s="0"/>
       <c r="K279" s="0"/>
       <c r="L279" s="0"/>
+      <c r="M279" s="0"/>
+      <c r="N279" s="0"/>
     </row>
     <row r="280">
-      <c r="A280" s="0" t="s">
-        <v>88</v>
-      </c>
+      <c r="A280" s="0"/>
       <c r="B280" s="0">
-        <v>0.27000000000000002</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="C280" s="0">
-        <v>0.01</v>
-      </c>
-      <c r="D280" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="E280" s="0"/>
-      <c r="F280" s="0"/>
-      <c r="G280" s="0"/>
-      <c r="H280" s="0"/>
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="D280" s="0">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="E280" s="0">
+        <v>0</v>
+      </c>
+      <c r="F280" s="0">
+        <v>2</v>
+      </c>
+      <c r="G280" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="H280" s="0">
+        <v>9.9999999999999996e-07</v>
+      </c>
       <c r="I280" s="0"/>
       <c r="J280" s="0"/>
       <c r="K280" s="0"/>
       <c r="L280" s="0"/>
+      <c r="M280" s="0"/>
+      <c r="N280" s="0"/>
     </row>
     <row r="281">
-      <c r="A281" s="0" t="s">
-        <v>103</v>
-      </c>
+      <c r="A281" s="0"/>
       <c r="B281" s="0">
+        <v>5</v>
+      </c>
+      <c r="C281" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="D281" s="0">
+        <v>0.96999999999999997</v>
+      </c>
+      <c r="E281" s="0">
         <v>0</v>
       </c>
-      <c r="C281" s="0">
-        <v>0</v>
-      </c>
-      <c r="D281" s="0" t="s">
-        <v>189</v>
-      </c>
-      <c r="E281" s="0"/>
-      <c r="F281" s="0"/>
-      <c r="G281" s="0"/>
-      <c r="H281" s="0"/>
+      <c r="F281" s="0">
+        <v>1</v>
+      </c>
+      <c r="G281" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="H281" s="0">
+        <v>9.9999999999999996e-07</v>
+      </c>
       <c r="I281" s="0"/>
       <c r="J281" s="0"/>
       <c r="K281" s="0"/>
       <c r="L281" s="0"/>
+      <c r="M281" s="0"/>
+      <c r="N281" s="0"/>
     </row>
     <row r="282">
-      <c r="A282" s="0" t="s">
-        <v>93</v>
-      </c>
+      <c r="A282" s="0"/>
       <c r="B282" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="C282" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="D282" s="0" t="s">
-        <v>180</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="C282" s="0"/>
+      <c r="D282" s="0"/>
       <c r="E282" s="0"/>
       <c r="F282" s="0"/>
-      <c r="G282" s="0"/>
+      <c r="G282" s="0" t="s">
+        <v>218</v>
+      </c>
       <c r="H282" s="0"/>
       <c r="I282" s="0"/>
       <c r="J282" s="0"/>
       <c r="K282" s="0"/>
       <c r="L282" s="0"/>
+      <c r="M282" s="0"/>
+      <c r="N282" s="0"/>
     </row>
     <row r="283">
       <c r="A283" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="B283" s="0">
-        <v>3600</v>
-      </c>
-      <c r="C283" s="0">
-        <v>3600</v>
-      </c>
-      <c r="D283" s="0" t="s">
-        <v>181</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B283" s="0"/>
+      <c r="C283" s="0"/>
+      <c r="D283" s="0"/>
       <c r="E283" s="0"/>
       <c r="F283" s="0"/>
-      <c r="G283" s="0"/>
+      <c r="G283" s="0" t="s">
+        <v>219</v>
+      </c>
       <c r="H283" s="0"/>
       <c r="I283" s="0"/>
       <c r="J283" s="0"/>
       <c r="K283" s="0"/>
       <c r="L283" s="0"/>
+      <c r="M283" s="0"/>
+      <c r="N283" s="0"/>
     </row>
     <row r="284">
-      <c r="A284" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="B284" s="0">
-        <v>50000</v>
-      </c>
-      <c r="C284" s="0">
-        <v>50000</v>
-      </c>
-      <c r="D284" s="0" t="s">
-        <v>182</v>
-      </c>
+      <c r="A284" s="0"/>
+      <c r="B284" s="0"/>
+      <c r="C284" s="0"/>
+      <c r="D284" s="0"/>
       <c r="E284" s="0"/>
       <c r="F284" s="0"/>
-      <c r="G284" s="0"/>
+      <c r="G284" s="0" t="s">
+        <v>220</v>
+      </c>
       <c r="H284" s="0"/>
       <c r="I284" s="0"/>
       <c r="J284" s="0"/>
       <c r="K284" s="0"/>
       <c r="L284" s="0"/>
+      <c r="M284" s="0"/>
+      <c r="N284" s="0"/>
     </row>
     <row r="285">
-      <c r="A285" s="0" t="s">
-        <v>8</v>
-      </c>
+      <c r="A285" s="0"/>
       <c r="B285" s="0"/>
       <c r="C285" s="0"/>
       <c r="D285" s="0"/>
@@ -5929,6 +6446,8 @@
       <c r="J285" s="0"/>
       <c r="K285" s="0"/>
       <c r="L285" s="0"/>
+      <c r="M285" s="0"/>
+      <c r="N285" s="0"/>
     </row>
     <row r="286">
       <c r="A286" s="0"/>
@@ -5943,9 +6462,13 @@
       <c r="J286" s="0"/>
       <c r="K286" s="0"/>
       <c r="L286" s="0"/>
+      <c r="M286" s="0"/>
+      <c r="N286" s="0"/>
     </row>
     <row r="287">
-      <c r="A287" s="0"/>
+      <c r="A287" s="0" t="s">
+        <v>0</v>
+      </c>
       <c r="B287" s="0"/>
       <c r="C287" s="0"/>
       <c r="D287" s="0"/>
@@ -5957,12 +6480,16 @@
       <c r="J287" s="0"/>
       <c r="K287" s="0"/>
       <c r="L287" s="0"/>
+      <c r="M287" s="0"/>
+      <c r="N287" s="0"/>
     </row>
     <row r="288">
       <c r="A288" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B288" s="0"/>
+        <v>79</v>
+      </c>
+      <c r="B288" s="0" t="s">
+        <v>133</v>
+      </c>
       <c r="C288" s="0"/>
       <c r="D288" s="0"/>
       <c r="E288" s="0"/>
@@ -5973,13 +6500,15 @@
       <c r="J288" s="0"/>
       <c r="K288" s="0"/>
       <c r="L288" s="0"/>
+      <c r="M288" s="0"/>
+      <c r="N288" s="0"/>
     </row>
     <row r="289">
       <c r="A289" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="B289" s="0" t="s">
-        <v>133</v>
+        <v>82</v>
+      </c>
+      <c r="B289" s="0">
+        <v>1</v>
       </c>
       <c r="C289" s="0"/>
       <c r="D289" s="0"/>
@@ -5991,14 +6520,12 @@
       <c r="J289" s="0"/>
       <c r="K289" s="0"/>
       <c r="L289" s="0"/>
+      <c r="M289" s="0"/>
+      <c r="N289" s="0"/>
     </row>
     <row r="290">
-      <c r="A290" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="B290" s="0">
-        <v>1</v>
-      </c>
+      <c r="A290" s="0"/>
+      <c r="B290" s="0"/>
       <c r="C290" s="0"/>
       <c r="D290" s="0"/>
       <c r="E290" s="0"/>
@@ -6009,14 +6536,22 @@
       <c r="J290" s="0"/>
       <c r="K290" s="0"/>
       <c r="L290" s="0"/>
+      <c r="M290" s="0"/>
+      <c r="N290" s="0"/>
     </row>
     <row r="291">
-      <c r="A291" s="0"/>
-      <c r="B291" s="0"/>
+      <c r="A291" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="B291" s="0" t="s">
+        <v>149</v>
+      </c>
       <c r="C291" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="D291" s="0"/>
+        <v>160</v>
+      </c>
+      <c r="D291" s="0" t="s">
+        <v>148</v>
+      </c>
       <c r="E291" s="0"/>
       <c r="F291" s="0"/>
       <c r="G291" s="0"/>
@@ -6025,20 +6560,18 @@
       <c r="J291" s="0"/>
       <c r="K291" s="0"/>
       <c r="L291" s="0"/>
+      <c r="M291" s="0"/>
+      <c r="N291" s="0"/>
     </row>
     <row r="292">
-      <c r="A292" s="0" t="s">
-        <v>87</v>
-      </c>
+      <c r="A292" s="0"/>
       <c r="B292" s="0">
-        <v>0.98999999999999999</v>
+        <v>0</v>
       </c>
       <c r="C292" s="0">
-        <v>0.98999999999999999</v>
-      </c>
-      <c r="D292" s="0" t="s">
-        <v>174</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="D292" s="0"/>
       <c r="E292" s="0"/>
       <c r="F292" s="0"/>
       <c r="G292" s="0"/>
@@ -6047,20 +6580,18 @@
       <c r="J292" s="0"/>
       <c r="K292" s="0"/>
       <c r="L292" s="0"/>
+      <c r="M292" s="0"/>
+      <c r="N292" s="0"/>
     </row>
     <row r="293">
-      <c r="A293" s="0" t="s">
-        <v>88</v>
-      </c>
+      <c r="A293" s="0"/>
       <c r="B293" s="0">
-        <v>0.001</v>
+        <v>100</v>
       </c>
       <c r="C293" s="0">
-        <v>0.01</v>
-      </c>
-      <c r="D293" s="0" t="s">
-        <v>175</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="D293" s="0"/>
       <c r="E293" s="0"/>
       <c r="F293" s="0"/>
       <c r="G293" s="0"/>
@@ -6069,20 +6600,16 @@
       <c r="J293" s="0"/>
       <c r="K293" s="0"/>
       <c r="L293" s="0"/>
+      <c r="M293" s="0"/>
+      <c r="N293" s="0"/>
     </row>
     <row r="294">
-      <c r="A294" s="0" t="s">
-        <v>106</v>
-      </c>
-      <c r="B294" s="0">
-        <v>0.70999999999999997</v>
-      </c>
-      <c r="C294" s="0">
-        <v>0.70999999999999997</v>
-      </c>
-      <c r="D294" s="0" t="s">
-        <v>190</v>
-      </c>
+      <c r="A294" s="0"/>
+      <c r="B294" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="C294" s="0"/>
+      <c r="D294" s="0"/>
       <c r="E294" s="0"/>
       <c r="F294" s="0"/>
       <c r="G294" s="0"/>
@@ -6091,20 +6618,16 @@
       <c r="J294" s="0"/>
       <c r="K294" s="0"/>
       <c r="L294" s="0"/>
+      <c r="M294" s="0"/>
+      <c r="N294" s="0"/>
     </row>
     <row r="295">
       <c r="A295" s="0" t="s">
-        <v>107</v>
-      </c>
-      <c r="B295" s="0">
-        <v>0.20999999999999999</v>
-      </c>
-      <c r="C295" s="0">
-        <v>0.20999999999999999</v>
-      </c>
-      <c r="D295" s="0" t="s">
-        <v>191</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B295" s="0"/>
+      <c r="C295" s="0"/>
+      <c r="D295" s="0"/>
       <c r="E295" s="0"/>
       <c r="F295" s="0"/>
       <c r="G295" s="0"/>
@@ -6113,16 +6636,14 @@
       <c r="J295" s="0"/>
       <c r="K295" s="0"/>
       <c r="L295" s="0"/>
+      <c r="M295" s="0"/>
+      <c r="N295" s="0"/>
     </row>
     <row r="296">
-      <c r="A296" s="0" t="s">
-        <v>108</v>
-      </c>
+      <c r="A296" s="0"/>
       <c r="B296" s="0"/>
       <c r="C296" s="0"/>
-      <c r="D296" s="0" t="s">
-        <v>192</v>
-      </c>
+      <c r="D296" s="0"/>
       <c r="E296" s="0"/>
       <c r="F296" s="0"/>
       <c r="G296" s="0"/>
@@ -6131,20 +6652,14 @@
       <c r="J296" s="0"/>
       <c r="K296" s="0"/>
       <c r="L296" s="0"/>
+      <c r="M296" s="0"/>
+      <c r="N296" s="0"/>
     </row>
     <row r="297">
-      <c r="A297" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="B297" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="C297" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="D297" s="0" t="s">
-        <v>193</v>
-      </c>
+      <c r="A297" s="0"/>
+      <c r="B297" s="0"/>
+      <c r="C297" s="0"/>
+      <c r="D297" s="0"/>
       <c r="E297" s="0"/>
       <c r="F297" s="0"/>
       <c r="G297" s="0"/>
@@ -6153,20 +6668,16 @@
       <c r="J297" s="0"/>
       <c r="K297" s="0"/>
       <c r="L297" s="0"/>
+      <c r="M297" s="0"/>
+      <c r="N297" s="0"/>
     </row>
     <row r="298">
       <c r="A298" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="B298" s="0">
-        <v>0.0001</v>
-      </c>
-      <c r="C298" s="0">
-        <v>0.0001</v>
-      </c>
-      <c r="D298" s="0" t="s">
-        <v>194</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B298" s="0"/>
+      <c r="C298" s="0"/>
+      <c r="D298" s="0"/>
       <c r="E298" s="0"/>
       <c r="F298" s="0"/>
       <c r="G298" s="0"/>
@@ -6175,20 +6686,18 @@
       <c r="J298" s="0"/>
       <c r="K298" s="0"/>
       <c r="L298" s="0"/>
+      <c r="M298" s="0"/>
+      <c r="N298" s="0"/>
     </row>
     <row r="299">
       <c r="A299" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="B299" s="0">
-        <v>0.01</v>
-      </c>
-      <c r="C299" s="0">
-        <v>0.02</v>
-      </c>
-      <c r="D299" s="0" t="s">
-        <v>195</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="B299" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="C299" s="0"/>
+      <c r="D299" s="0"/>
       <c r="E299" s="0"/>
       <c r="F299" s="0"/>
       <c r="G299" s="0"/>
@@ -6197,20 +6706,18 @@
       <c r="J299" s="0"/>
       <c r="K299" s="0"/>
       <c r="L299" s="0"/>
+      <c r="M299" s="0"/>
+      <c r="N299" s="0"/>
     </row>
     <row r="300">
       <c r="A300" s="0" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="B300" s="0">
-        <v>0</v>
-      </c>
-      <c r="C300" s="0">
-        <v>0</v>
-      </c>
-      <c r="D300" s="0" t="s">
-        <v>196</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C300" s="0"/>
+      <c r="D300" s="0"/>
       <c r="E300" s="0"/>
       <c r="F300" s="0"/>
       <c r="G300" s="0"/>
@@ -6219,20 +6726,16 @@
       <c r="J300" s="0"/>
       <c r="K300" s="0"/>
       <c r="L300" s="0"/>
+      <c r="M300" s="0"/>
+      <c r="N300" s="0"/>
     </row>
     <row r="301">
-      <c r="A301" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="B301" s="0">
-        <v>16</v>
-      </c>
-      <c r="C301" s="0">
-        <v>48</v>
-      </c>
-      <c r="D301" s="0" t="s">
-        <v>197</v>
-      </c>
+      <c r="A301" s="0"/>
+      <c r="B301" s="0"/>
+      <c r="C301" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="D301" s="0"/>
       <c r="E301" s="0"/>
       <c r="F301" s="0"/>
       <c r="G301" s="0"/>
@@ -6241,19 +6744,21 @@
       <c r="J301" s="0"/>
       <c r="K301" s="0"/>
       <c r="L301" s="0"/>
+      <c r="M301" s="0"/>
+      <c r="N301" s="0"/>
     </row>
     <row r="302">
       <c r="A302" s="0" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="B302" s="0">
-        <v>600</v>
+        <v>0.25</v>
       </c>
       <c r="C302" s="0">
-        <v>350</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="D302" s="0" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="E302" s="0"/>
       <c r="F302" s="0"/>
@@ -6263,19 +6768,21 @@
       <c r="J302" s="0"/>
       <c r="K302" s="0"/>
       <c r="L302" s="0"/>
+      <c r="M302" s="0"/>
+      <c r="N302" s="0"/>
     </row>
     <row r="303">
       <c r="A303" s="0" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="B303" s="0">
-        <v>52</v>
+        <v>0.98999999999999999</v>
       </c>
       <c r="C303" s="0">
-        <v>26</v>
+        <v>0.98999999999999999</v>
       </c>
       <c r="D303" s="0" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="E303" s="0"/>
       <c r="F303" s="0"/>
@@ -6285,17 +6792,21 @@
       <c r="J303" s="0"/>
       <c r="K303" s="0"/>
       <c r="L303" s="0"/>
+      <c r="M303" s="0"/>
+      <c r="N303" s="0"/>
     </row>
     <row r="304">
       <c r="A304" s="0" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="B304" s="0">
-        <v>0.001</v>
-      </c>
-      <c r="C304" s="0"/>
+        <v>0.27000000000000002</v>
+      </c>
+      <c r="C304" s="0">
+        <v>0.01</v>
+      </c>
       <c r="D304" s="0" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="E304" s="0"/>
       <c r="F304" s="0"/>
@@ -6305,19 +6816,21 @@
       <c r="J304" s="0"/>
       <c r="K304" s="0"/>
       <c r="L304" s="0"/>
+      <c r="M304" s="0"/>
+      <c r="N304" s="0"/>
     </row>
     <row r="305">
       <c r="A305" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="B305" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="C305" s="0" t="s">
-        <v>160</v>
+        <v>89</v>
+      </c>
+      <c r="B305" s="0">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="C305" s="0">
+        <v>0.10000000000000001</v>
       </c>
       <c r="D305" s="0" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E305" s="0"/>
       <c r="F305" s="0"/>
@@ -6327,19 +6840,21 @@
       <c r="J305" s="0"/>
       <c r="K305" s="0"/>
       <c r="L305" s="0"/>
+      <c r="M305" s="0"/>
+      <c r="N305" s="0"/>
     </row>
     <row r="306">
       <c r="A306" s="0" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B306" s="0">
-        <v>3600</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="C306" s="0">
-        <v>3600</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="D306" s="0" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E306" s="0"/>
       <c r="F306" s="0"/>
@@ -6349,19 +6864,21 @@
       <c r="J306" s="0"/>
       <c r="K306" s="0"/>
       <c r="L306" s="0"/>
+      <c r="M306" s="0"/>
+      <c r="N306" s="0"/>
     </row>
     <row r="307">
       <c r="A307" s="0" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B307" s="0">
-        <v>50000</v>
+        <v>0.5</v>
       </c>
       <c r="C307" s="0">
-        <v>50000</v>
+        <v>0.5</v>
       </c>
       <c r="D307" s="0" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E307" s="0"/>
       <c r="F307" s="0"/>
@@ -6371,14 +6888,22 @@
       <c r="J307" s="0"/>
       <c r="K307" s="0"/>
       <c r="L307" s="0"/>
+      <c r="M307" s="0"/>
+      <c r="N307" s="0"/>
     </row>
     <row r="308">
       <c r="A308" s="0" t="s">
-        <v>116</v>
-      </c>
-      <c r="B308" s="0"/>
-      <c r="C308" s="0"/>
-      <c r="D308" s="0"/>
+        <v>92</v>
+      </c>
+      <c r="B308" s="0">
+        <v>1.0000000000000001e-05</v>
+      </c>
+      <c r="C308" s="0">
+        <v>1.0000000000000001e-05</v>
+      </c>
+      <c r="D308" s="0" t="s">
+        <v>180</v>
+      </c>
       <c r="E308" s="0"/>
       <c r="F308" s="0"/>
       <c r="G308" s="0"/>
@@ -6387,14 +6912,22 @@
       <c r="J308" s="0"/>
       <c r="K308" s="0"/>
       <c r="L308" s="0"/>
+      <c r="M308" s="0"/>
+      <c r="N308" s="0"/>
     </row>
     <row r="309">
       <c r="A309" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B309" s="0"/>
-      <c r="C309" s="0"/>
-      <c r="D309" s="0"/>
+        <v>93</v>
+      </c>
+      <c r="B309" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="C309" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="D309" s="0" t="s">
+        <v>181</v>
+      </c>
       <c r="E309" s="0"/>
       <c r="F309" s="0"/>
       <c r="G309" s="0"/>
@@ -6403,12 +6936,22 @@
       <c r="J309" s="0"/>
       <c r="K309" s="0"/>
       <c r="L309" s="0"/>
+      <c r="M309" s="0"/>
+      <c r="N309" s="0"/>
     </row>
     <row r="310">
-      <c r="A310" s="0"/>
-      <c r="B310" s="0"/>
-      <c r="C310" s="0"/>
-      <c r="D310" s="0"/>
+      <c r="A310" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="B310" s="0">
+        <v>3600</v>
+      </c>
+      <c r="C310" s="0">
+        <v>3600</v>
+      </c>
+      <c r="D310" s="0" t="s">
+        <v>182</v>
+      </c>
       <c r="E310" s="0"/>
       <c r="F310" s="0"/>
       <c r="G310" s="0"/>
@@ -6417,12 +6960,22 @@
       <c r="J310" s="0"/>
       <c r="K310" s="0"/>
       <c r="L310" s="0"/>
+      <c r="M310" s="0"/>
+      <c r="N310" s="0"/>
     </row>
     <row r="311">
-      <c r="A311" s="0"/>
-      <c r="B311" s="0"/>
-      <c r="C311" s="0"/>
-      <c r="D311" s="0"/>
+      <c r="A311" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B311" s="0">
+        <v>50000</v>
+      </c>
+      <c r="C311" s="0">
+        <v>50000</v>
+      </c>
+      <c r="D311" s="0" t="s">
+        <v>183</v>
+      </c>
       <c r="E311" s="0"/>
       <c r="F311" s="0"/>
       <c r="G311" s="0"/>
@@ -6431,14 +6984,22 @@
       <c r="J311" s="0"/>
       <c r="K311" s="0"/>
       <c r="L311" s="0"/>
+      <c r="M311" s="0"/>
+      <c r="N311" s="0"/>
     </row>
     <row r="312">
       <c r="A312" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B312" s="0"/>
-      <c r="C312" s="0"/>
-      <c r="D312" s="0"/>
+        <v>96</v>
+      </c>
+      <c r="B312" s="0">
+        <v>1000</v>
+      </c>
+      <c r="C312" s="0">
+        <v>1000</v>
+      </c>
+      <c r="D312" s="0" t="s">
+        <v>184</v>
+      </c>
       <c r="E312" s="0"/>
       <c r="F312" s="0"/>
       <c r="G312" s="0"/>
@@ -6447,16 +7008,22 @@
       <c r="J312" s="0"/>
       <c r="K312" s="0"/>
       <c r="L312" s="0"/>
+      <c r="M312" s="0"/>
+      <c r="N312" s="0"/>
     </row>
     <row r="313">
       <c r="A313" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="B313" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="C313" s="0"/>
-      <c r="D313" s="0"/>
+        <v>97</v>
+      </c>
+      <c r="B313" s="0">
+        <v>1000</v>
+      </c>
+      <c r="C313" s="0">
+        <v>1000</v>
+      </c>
+      <c r="D313" s="0" t="s">
+        <v>185</v>
+      </c>
       <c r="E313" s="0"/>
       <c r="F313" s="0"/>
       <c r="G313" s="0"/>
@@ -6465,17 +7032,21 @@
       <c r="J313" s="0"/>
       <c r="K313" s="0"/>
       <c r="L313" s="0"/>
+      <c r="M313" s="0"/>
+      <c r="N313" s="0"/>
     </row>
     <row r="314">
       <c r="A314" s="0" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="B314" s="0">
-        <v>1</v>
-      </c>
-      <c r="C314" s="0"/>
+        <v>-40</v>
+      </c>
+      <c r="C314" s="0">
+        <v>-50</v>
+      </c>
       <c r="D314" s="0" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="E314" s="0"/>
       <c r="F314" s="0"/>
@@ -6485,14 +7056,22 @@
       <c r="J314" s="0"/>
       <c r="K314" s="0"/>
       <c r="L314" s="0"/>
+      <c r="M314" s="0"/>
+      <c r="N314" s="0"/>
     </row>
     <row r="315">
-      <c r="A315" s="0"/>
-      <c r="B315" s="0"/>
-      <c r="C315" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="D315" s="0"/>
+      <c r="A315" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B315" s="0">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="C315" s="0">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="D315" s="0" t="s">
+        <v>187</v>
+      </c>
       <c r="E315" s="0"/>
       <c r="F315" s="0"/>
       <c r="G315" s="0"/>
@@ -6501,19 +7080,21 @@
       <c r="J315" s="0"/>
       <c r="K315" s="0"/>
       <c r="L315" s="0"/>
+      <c r="M315" s="0"/>
+      <c r="N315" s="0"/>
     </row>
     <row r="316">
       <c r="A316" s="0" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="B316" s="0">
-        <v>0.25</v>
+        <v>0.96999999999999997</v>
       </c>
       <c r="C316" s="0">
-        <v>0.25</v>
+        <v>0.96999999999999997</v>
       </c>
       <c r="D316" s="0" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="E316" s="0"/>
       <c r="F316" s="0"/>
@@ -6523,14 +7104,22 @@
       <c r="J316" s="0"/>
       <c r="K316" s="0"/>
       <c r="L316" s="0"/>
+      <c r="M316" s="0"/>
+      <c r="N316" s="0"/>
     </row>
     <row r="317">
       <c r="A317" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B317" s="0"/>
-      <c r="C317" s="0"/>
-      <c r="D317" s="0"/>
+        <v>101</v>
+      </c>
+      <c r="B317" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="C317" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="D317" s="0" t="s">
+        <v>189</v>
+      </c>
       <c r="E317" s="0"/>
       <c r="F317" s="0"/>
       <c r="G317" s="0"/>
@@ -6539,9 +7128,13 @@
       <c r="J317" s="0"/>
       <c r="K317" s="0"/>
       <c r="L317" s="0"/>
+      <c r="M317" s="0"/>
+      <c r="N317" s="0"/>
     </row>
     <row r="318">
-      <c r="A318" s="0"/>
+      <c r="A318" s="0" t="s">
+        <v>8</v>
+      </c>
       <c r="B318" s="0"/>
       <c r="C318" s="0"/>
       <c r="D318" s="0"/>
@@ -6553,6 +7146,8 @@
       <c r="J318" s="0"/>
       <c r="K318" s="0"/>
       <c r="L318" s="0"/>
+      <c r="M318" s="0"/>
+      <c r="N318" s="0"/>
     </row>
     <row r="319">
       <c r="A319" s="0"/>
@@ -6567,11 +7162,11 @@
       <c r="J319" s="0"/>
       <c r="K319" s="0"/>
       <c r="L319" s="0"/>
+      <c r="M319" s="0"/>
+      <c r="N319" s="0"/>
     </row>
     <row r="320">
-      <c r="A320" s="0" t="s">
-        <v>0</v>
-      </c>
+      <c r="A320" s="0"/>
       <c r="B320" s="0"/>
       <c r="C320" s="0"/>
       <c r="D320" s="0"/>
@@ -6583,14 +7178,14 @@
       <c r="J320" s="0"/>
       <c r="K320" s="0"/>
       <c r="L320" s="0"/>
+      <c r="M320" s="0"/>
+      <c r="N320" s="0"/>
     </row>
     <row r="321">
       <c r="A321" s="0" t="s">
-        <v>120</v>
-      </c>
-      <c r="B321" s="0" t="s">
-        <v>133</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B321" s="0"/>
       <c r="C321" s="0"/>
       <c r="D321" s="0"/>
       <c r="E321" s="0"/>
@@ -6601,13 +7196,15 @@
       <c r="J321" s="0"/>
       <c r="K321" s="0"/>
       <c r="L321" s="0"/>
+      <c r="M321" s="0"/>
+      <c r="N321" s="0"/>
     </row>
     <row r="322">
       <c r="A322" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="B322" s="0">
-        <v>1</v>
+        <v>84</v>
+      </c>
+      <c r="B322" s="0" t="s">
+        <v>133</v>
       </c>
       <c r="C322" s="0"/>
       <c r="D322" s="0"/>
@@ -6619,13 +7216,17 @@
       <c r="J322" s="0"/>
       <c r="K322" s="0"/>
       <c r="L322" s="0"/>
+      <c r="M322" s="0"/>
+      <c r="N322" s="0"/>
     </row>
     <row r="323">
-      <c r="A323" s="0"/>
-      <c r="B323" s="0"/>
-      <c r="C323" s="0" t="s">
-        <v>155</v>
-      </c>
+      <c r="A323" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B323" s="0">
+        <v>1</v>
+      </c>
+      <c r="C323" s="0"/>
       <c r="D323" s="0"/>
       <c r="E323" s="0"/>
       <c r="F323" s="0"/>
@@ -6635,20 +7236,16 @@
       <c r="J323" s="0"/>
       <c r="K323" s="0"/>
       <c r="L323" s="0"/>
+      <c r="M323" s="0"/>
+      <c r="N323" s="0"/>
     </row>
     <row r="324">
-      <c r="A324" s="0" t="s">
-        <v>122</v>
-      </c>
-      <c r="B324" s="0">
-        <v>20</v>
-      </c>
-      <c r="C324" s="0">
-        <v>10000</v>
-      </c>
-      <c r="D324" s="0" t="s">
-        <v>203</v>
-      </c>
+      <c r="A324" s="0"/>
+      <c r="B324" s="0"/>
+      <c r="C324" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="D324" s="0"/>
       <c r="E324" s="0"/>
       <c r="F324" s="0"/>
       <c r="G324" s="0"/>
@@ -6657,19 +7254,21 @@
       <c r="J324" s="0"/>
       <c r="K324" s="0"/>
       <c r="L324" s="0"/>
+      <c r="M324" s="0"/>
+      <c r="N324" s="0"/>
     </row>
     <row r="325">
       <c r="A325" s="0" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="B325" s="0">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C325" s="0">
-        <v>0</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="D325" s="0" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="E325" s="0"/>
       <c r="F325" s="0"/>
@@ -6679,19 +7278,21 @@
       <c r="J325" s="0"/>
       <c r="K325" s="0"/>
       <c r="L325" s="0"/>
+      <c r="M325" s="0"/>
+      <c r="N325" s="0"/>
     </row>
     <row r="326">
       <c r="A326" s="0" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="B326" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.98999999999999999</v>
       </c>
       <c r="C326" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.98999999999999999</v>
       </c>
       <c r="D326" s="0" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="E326" s="0"/>
       <c r="F326" s="0"/>
@@ -6701,19 +7302,21 @@
       <c r="J326" s="0"/>
       <c r="K326" s="0"/>
       <c r="L326" s="0"/>
+      <c r="M326" s="0"/>
+      <c r="N326" s="0"/>
     </row>
     <row r="327">
       <c r="A327" s="0" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="B327" s="0">
-        <v>5</v>
+        <v>0.27000000000000002</v>
       </c>
       <c r="C327" s="0">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="D327" s="0" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="E327" s="0"/>
       <c r="F327" s="0"/>
@@ -6723,19 +7326,21 @@
       <c r="J327" s="0"/>
       <c r="K327" s="0"/>
       <c r="L327" s="0"/>
+      <c r="M327" s="0"/>
+      <c r="N327" s="0"/>
     </row>
     <row r="328">
       <c r="A328" s="0" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="B328" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C328" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D328" s="0" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="E328" s="0"/>
       <c r="F328" s="0"/>
@@ -6745,14 +7350,22 @@
       <c r="J328" s="0"/>
       <c r="K328" s="0"/>
       <c r="L328" s="0"/>
+      <c r="M328" s="0"/>
+      <c r="N328" s="0"/>
     </row>
     <row r="329">
       <c r="A329" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B329" s="0"/>
-      <c r="C329" s="0"/>
-      <c r="D329" s="0"/>
+        <v>93</v>
+      </c>
+      <c r="B329" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="C329" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="D329" s="0" t="s">
+        <v>181</v>
+      </c>
       <c r="E329" s="0"/>
       <c r="F329" s="0"/>
       <c r="G329" s="0"/>
@@ -6761,12 +7374,22 @@
       <c r="J329" s="0"/>
       <c r="K329" s="0"/>
       <c r="L329" s="0"/>
+      <c r="M329" s="0"/>
+      <c r="N329" s="0"/>
     </row>
     <row r="330">
-      <c r="A330" s="0"/>
-      <c r="B330" s="0"/>
-      <c r="C330" s="0"/>
-      <c r="D330" s="0"/>
+      <c r="A330" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="B330" s="0">
+        <v>3600</v>
+      </c>
+      <c r="C330" s="0">
+        <v>3600</v>
+      </c>
+      <c r="D330" s="0" t="s">
+        <v>182</v>
+      </c>
       <c r="E330" s="0"/>
       <c r="F330" s="0"/>
       <c r="G330" s="0"/>
@@ -6775,12 +7398,22 @@
       <c r="J330" s="0"/>
       <c r="K330" s="0"/>
       <c r="L330" s="0"/>
+      <c r="M330" s="0"/>
+      <c r="N330" s="0"/>
     </row>
     <row r="331">
-      <c r="A331" s="0"/>
-      <c r="B331" s="0"/>
-      <c r="C331" s="0"/>
-      <c r="D331" s="0"/>
+      <c r="A331" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B331" s="0">
+        <v>50000</v>
+      </c>
+      <c r="C331" s="0">
+        <v>50000</v>
+      </c>
+      <c r="D331" s="0" t="s">
+        <v>183</v>
+      </c>
       <c r="E331" s="0"/>
       <c r="F331" s="0"/>
       <c r="G331" s="0"/>
@@ -6789,10 +7422,12 @@
       <c r="J331" s="0"/>
       <c r="K331" s="0"/>
       <c r="L331" s="0"/>
+      <c r="M331" s="0"/>
+      <c r="N331" s="0"/>
     </row>
     <row r="332">
       <c r="A332" s="0" t="s">
-        <v>127</v>
+        <v>8</v>
       </c>
       <c r="B332" s="0"/>
       <c r="C332" s="0"/>
@@ -6805,14 +7440,12 @@
       <c r="J332" s="0"/>
       <c r="K332" s="0"/>
       <c r="L332" s="0"/>
+      <c r="M332" s="0"/>
+      <c r="N332" s="0"/>
     </row>
     <row r="333">
-      <c r="A333" s="0" t="s">
-        <v>120</v>
-      </c>
-      <c r="B333" s="0" t="s">
-        <v>133</v>
-      </c>
+      <c r="A333" s="0"/>
+      <c r="B333" s="0"/>
       <c r="C333" s="0"/>
       <c r="D333" s="0"/>
       <c r="E333" s="0"/>
@@ -6823,14 +7456,12 @@
       <c r="J333" s="0"/>
       <c r="K333" s="0"/>
       <c r="L333" s="0"/>
+      <c r="M333" s="0"/>
+      <c r="N333" s="0"/>
     </row>
     <row r="334">
-      <c r="A334" s="0" t="s">
-        <v>128</v>
-      </c>
-      <c r="B334" s="0">
-        <v>1</v>
-      </c>
+      <c r="A334" s="0"/>
+      <c r="B334" s="0"/>
       <c r="C334" s="0"/>
       <c r="D334" s="0"/>
       <c r="E334" s="0"/>
@@ -6841,18 +7472,16 @@
       <c r="J334" s="0"/>
       <c r="K334" s="0"/>
       <c r="L334" s="0"/>
+      <c r="M334" s="0"/>
+      <c r="N334" s="0"/>
     </row>
     <row r="335">
       <c r="A335" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="B335" s="0">
-        <v>3034</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B335" s="0"/>
       <c r="C335" s="0"/>
-      <c r="D335" s="0" t="s">
-        <v>208</v>
-      </c>
+      <c r="D335" s="0"/>
       <c r="E335" s="0"/>
       <c r="F335" s="0"/>
       <c r="G335" s="0"/>
@@ -6861,12 +7490,16 @@
       <c r="J335" s="0"/>
       <c r="K335" s="0"/>
       <c r="L335" s="0"/>
+      <c r="M335" s="0"/>
+      <c r="N335" s="0"/>
     </row>
     <row r="336">
       <c r="A336" s="0" t="s">
-        <v>130</v>
-      </c>
-      <c r="B336" s="0"/>
+        <v>104</v>
+      </c>
+      <c r="B336" s="0" t="s">
+        <v>133</v>
+      </c>
       <c r="C336" s="0"/>
       <c r="D336" s="0"/>
       <c r="E336" s="0"/>
@@ -6877,13 +7510,15 @@
       <c r="J336" s="0"/>
       <c r="K336" s="0"/>
       <c r="L336" s="0"/>
+      <c r="M336" s="0"/>
+      <c r="N336" s="0"/>
     </row>
     <row r="337">
       <c r="A337" s="0" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="B337" s="0">
-        <v>0.029999999999999999</v>
+        <v>1</v>
       </c>
       <c r="C337" s="0"/>
       <c r="D337" s="0"/>
@@ -6895,15 +7530,15 @@
       <c r="J337" s="0"/>
       <c r="K337" s="0"/>
       <c r="L337" s="0"/>
+      <c r="M337" s="0"/>
+      <c r="N337" s="0"/>
     </row>
     <row r="338">
-      <c r="A338" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="B338" s="0">
-        <v>50</v>
-      </c>
-      <c r="C338" s="0"/>
+      <c r="A338" s="0"/>
+      <c r="B338" s="0"/>
+      <c r="C338" s="0" t="s">
+        <v>156</v>
+      </c>
       <c r="D338" s="0"/>
       <c r="E338" s="0"/>
       <c r="F338" s="0"/>
@@ -6913,17 +7548,21 @@
       <c r="J338" s="0"/>
       <c r="K338" s="0"/>
       <c r="L338" s="0"/>
+      <c r="M338" s="0"/>
+      <c r="N338" s="0"/>
     </row>
     <row r="339">
       <c r="A339" s="0" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="B339" s="0">
-        <v>1</v>
-      </c>
-      <c r="C339" s="0"/>
+        <v>0.98999999999999999</v>
+      </c>
+      <c r="C339" s="0">
+        <v>0.98999999999999999</v>
+      </c>
       <c r="D339" s="0" t="s">
-        <v>209</v>
+        <v>175</v>
       </c>
       <c r="E339" s="0"/>
       <c r="F339" s="0"/>
@@ -6933,14 +7572,22 @@
       <c r="J339" s="0"/>
       <c r="K339" s="0"/>
       <c r="L339" s="0"/>
+      <c r="M339" s="0"/>
+      <c r="N339" s="0"/>
     </row>
     <row r="340">
       <c r="A340" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B340" s="0"/>
-      <c r="C340" s="0"/>
-      <c r="D340" s="0"/>
+        <v>88</v>
+      </c>
+      <c r="B340" s="0">
+        <v>0.001</v>
+      </c>
+      <c r="C340" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="D340" s="0" t="s">
+        <v>176</v>
+      </c>
       <c r="E340" s="0"/>
       <c r="F340" s="0"/>
       <c r="G340" s="0"/>
@@ -6949,12 +7596,22 @@
       <c r="J340" s="0"/>
       <c r="K340" s="0"/>
       <c r="L340" s="0"/>
+      <c r="M340" s="0"/>
+      <c r="N340" s="0"/>
     </row>
     <row r="341">
-      <c r="A341" s="0"/>
-      <c r="B341" s="0"/>
-      <c r="C341" s="0"/>
-      <c r="D341" s="0"/>
+      <c r="A341" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="B341" s="0">
+        <v>0.70999999999999997</v>
+      </c>
+      <c r="C341" s="0">
+        <v>0.70999999999999997</v>
+      </c>
+      <c r="D341" s="0" t="s">
+        <v>191</v>
+      </c>
       <c r="E341" s="0"/>
       <c r="F341" s="0"/>
       <c r="G341" s="0"/>
@@ -6963,12 +7620,22 @@
       <c r="J341" s="0"/>
       <c r="K341" s="0"/>
       <c r="L341" s="0"/>
+      <c r="M341" s="0"/>
+      <c r="N341" s="0"/>
     </row>
     <row r="342">
-      <c r="A342" s="0"/>
-      <c r="B342" s="0"/>
-      <c r="C342" s="0"/>
-      <c r="D342" s="0"/>
+      <c r="A342" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="B342" s="0">
+        <v>0.20999999999999999</v>
+      </c>
+      <c r="C342" s="0">
+        <v>0.20999999999999999</v>
+      </c>
+      <c r="D342" s="0" t="s">
+        <v>192</v>
+      </c>
       <c r="E342" s="0"/>
       <c r="F342" s="0"/>
       <c r="G342" s="0"/>
@@ -6977,6 +7644,966 @@
       <c r="J342" s="0"/>
       <c r="K342" s="0"/>
       <c r="L342" s="0"/>
+      <c r="M342" s="0"/>
+      <c r="N342" s="0"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="B343" s="0"/>
+      <c r="C343" s="0"/>
+      <c r="D343" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="E343" s="0"/>
+      <c r="F343" s="0"/>
+      <c r="G343" s="0"/>
+      <c r="H343" s="0"/>
+      <c r="I343" s="0"/>
+      <c r="J343" s="0"/>
+      <c r="K343" s="0"/>
+      <c r="L343" s="0"/>
+      <c r="M343" s="0"/>
+      <c r="N343" s="0"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="B344" s="0">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="C344" s="0">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="D344" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="E344" s="0"/>
+      <c r="F344" s="0"/>
+      <c r="G344" s="0"/>
+      <c r="H344" s="0"/>
+      <c r="I344" s="0"/>
+      <c r="J344" s="0"/>
+      <c r="K344" s="0"/>
+      <c r="L344" s="0"/>
+      <c r="M344" s="0"/>
+      <c r="N344" s="0"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B345" s="0">
+        <v>0.0001</v>
+      </c>
+      <c r="C345" s="0">
+        <v>0.0001</v>
+      </c>
+      <c r="D345" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="E345" s="0"/>
+      <c r="F345" s="0"/>
+      <c r="G345" s="0"/>
+      <c r="H345" s="0"/>
+      <c r="I345" s="0"/>
+      <c r="J345" s="0"/>
+      <c r="K345" s="0"/>
+      <c r="L345" s="0"/>
+      <c r="M345" s="0"/>
+      <c r="N345" s="0"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="B346" s="0">
+        <v>0.01</v>
+      </c>
+      <c r="C346" s="0">
+        <v>0.02</v>
+      </c>
+      <c r="D346" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="E346" s="0"/>
+      <c r="F346" s="0"/>
+      <c r="G346" s="0"/>
+      <c r="H346" s="0"/>
+      <c r="I346" s="0"/>
+      <c r="J346" s="0"/>
+      <c r="K346" s="0"/>
+      <c r="L346" s="0"/>
+      <c r="M346" s="0"/>
+      <c r="N346" s="0"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="B347" s="0">
+        <v>0</v>
+      </c>
+      <c r="C347" s="0">
+        <v>0</v>
+      </c>
+      <c r="D347" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="E347" s="0"/>
+      <c r="F347" s="0"/>
+      <c r="G347" s="0"/>
+      <c r="H347" s="0"/>
+      <c r="I347" s="0"/>
+      <c r="J347" s="0"/>
+      <c r="K347" s="0"/>
+      <c r="L347" s="0"/>
+      <c r="M347" s="0"/>
+      <c r="N347" s="0"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B348" s="0">
+        <v>16</v>
+      </c>
+      <c r="C348" s="0">
+        <v>48</v>
+      </c>
+      <c r="D348" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="E348" s="0"/>
+      <c r="F348" s="0"/>
+      <c r="G348" s="0"/>
+      <c r="H348" s="0"/>
+      <c r="I348" s="0"/>
+      <c r="J348" s="0"/>
+      <c r="K348" s="0"/>
+      <c r="L348" s="0"/>
+      <c r="M348" s="0"/>
+      <c r="N348" s="0"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="B349" s="0">
+        <v>600</v>
+      </c>
+      <c r="C349" s="0">
+        <v>350</v>
+      </c>
+      <c r="D349" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="E349" s="0"/>
+      <c r="F349" s="0"/>
+      <c r="G349" s="0"/>
+      <c r="H349" s="0"/>
+      <c r="I349" s="0"/>
+      <c r="J349" s="0"/>
+      <c r="K349" s="0"/>
+      <c r="L349" s="0"/>
+      <c r="M349" s="0"/>
+      <c r="N349" s="0"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="B350" s="0">
+        <v>52</v>
+      </c>
+      <c r="C350" s="0">
+        <v>26</v>
+      </c>
+      <c r="D350" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="E350" s="0"/>
+      <c r="F350" s="0"/>
+      <c r="G350" s="0"/>
+      <c r="H350" s="0"/>
+      <c r="I350" s="0"/>
+      <c r="J350" s="0"/>
+      <c r="K350" s="0"/>
+      <c r="L350" s="0"/>
+      <c r="M350" s="0"/>
+      <c r="N350" s="0"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="B351" s="0">
+        <v>0.001</v>
+      </c>
+      <c r="C351" s="0"/>
+      <c r="D351" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="E351" s="0"/>
+      <c r="F351" s="0"/>
+      <c r="G351" s="0"/>
+      <c r="H351" s="0"/>
+      <c r="I351" s="0"/>
+      <c r="J351" s="0"/>
+      <c r="K351" s="0"/>
+      <c r="L351" s="0"/>
+      <c r="M351" s="0"/>
+      <c r="N351" s="0"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="B352" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="C352" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="D352" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="E352" s="0"/>
+      <c r="F352" s="0"/>
+      <c r="G352" s="0"/>
+      <c r="H352" s="0"/>
+      <c r="I352" s="0"/>
+      <c r="J352" s="0"/>
+      <c r="K352" s="0"/>
+      <c r="L352" s="0"/>
+      <c r="M352" s="0"/>
+      <c r="N352" s="0"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="B353" s="0">
+        <v>3600</v>
+      </c>
+      <c r="C353" s="0">
+        <v>3600</v>
+      </c>
+      <c r="D353" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="E353" s="0"/>
+      <c r="F353" s="0"/>
+      <c r="G353" s="0"/>
+      <c r="H353" s="0"/>
+      <c r="I353" s="0"/>
+      <c r="J353" s="0"/>
+      <c r="K353" s="0"/>
+      <c r="L353" s="0"/>
+      <c r="M353" s="0"/>
+      <c r="N353" s="0"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B354" s="0">
+        <v>50000</v>
+      </c>
+      <c r="C354" s="0">
+        <v>50000</v>
+      </c>
+      <c r="D354" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="E354" s="0"/>
+      <c r="F354" s="0"/>
+      <c r="G354" s="0"/>
+      <c r="H354" s="0"/>
+      <c r="I354" s="0"/>
+      <c r="J354" s="0"/>
+      <c r="K354" s="0"/>
+      <c r="L354" s="0"/>
+      <c r="M354" s="0"/>
+      <c r="N354" s="0"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="B355" s="0"/>
+      <c r="C355" s="0"/>
+      <c r="D355" s="0"/>
+      <c r="E355" s="0"/>
+      <c r="F355" s="0"/>
+      <c r="G355" s="0"/>
+      <c r="H355" s="0"/>
+      <c r="I355" s="0"/>
+      <c r="J355" s="0"/>
+      <c r="K355" s="0"/>
+      <c r="L355" s="0"/>
+      <c r="M355" s="0"/>
+      <c r="N355" s="0"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B356" s="0"/>
+      <c r="C356" s="0"/>
+      <c r="D356" s="0"/>
+      <c r="E356" s="0"/>
+      <c r="F356" s="0"/>
+      <c r="G356" s="0"/>
+      <c r="H356" s="0"/>
+      <c r="I356" s="0"/>
+      <c r="J356" s="0"/>
+      <c r="K356" s="0"/>
+      <c r="L356" s="0"/>
+      <c r="M356" s="0"/>
+      <c r="N356" s="0"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="0"/>
+      <c r="B357" s="0"/>
+      <c r="C357" s="0"/>
+      <c r="D357" s="0"/>
+      <c r="E357" s="0"/>
+      <c r="F357" s="0"/>
+      <c r="G357" s="0"/>
+      <c r="H357" s="0"/>
+      <c r="I357" s="0"/>
+      <c r="J357" s="0"/>
+      <c r="K357" s="0"/>
+      <c r="L357" s="0"/>
+      <c r="M357" s="0"/>
+      <c r="N357" s="0"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="0"/>
+      <c r="B358" s="0"/>
+      <c r="C358" s="0"/>
+      <c r="D358" s="0"/>
+      <c r="E358" s="0"/>
+      <c r="F358" s="0"/>
+      <c r="G358" s="0"/>
+      <c r="H358" s="0"/>
+      <c r="I358" s="0"/>
+      <c r="J358" s="0"/>
+      <c r="K358" s="0"/>
+      <c r="L358" s="0"/>
+      <c r="M358" s="0"/>
+      <c r="N358" s="0"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B359" s="0"/>
+      <c r="C359" s="0"/>
+      <c r="D359" s="0"/>
+      <c r="E359" s="0"/>
+      <c r="F359" s="0"/>
+      <c r="G359" s="0"/>
+      <c r="H359" s="0"/>
+      <c r="I359" s="0"/>
+      <c r="J359" s="0"/>
+      <c r="K359" s="0"/>
+      <c r="L359" s="0"/>
+      <c r="M359" s="0"/>
+      <c r="N359" s="0"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="B360" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="C360" s="0"/>
+      <c r="D360" s="0"/>
+      <c r="E360" s="0"/>
+      <c r="F360" s="0"/>
+      <c r="G360" s="0"/>
+      <c r="H360" s="0"/>
+      <c r="I360" s="0"/>
+      <c r="J360" s="0"/>
+      <c r="K360" s="0"/>
+      <c r="L360" s="0"/>
+      <c r="M360" s="0"/>
+      <c r="N360" s="0"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="B361" s="0">
+        <v>1</v>
+      </c>
+      <c r="C361" s="0"/>
+      <c r="D361" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E361" s="0"/>
+      <c r="F361" s="0"/>
+      <c r="G361" s="0"/>
+      <c r="H361" s="0"/>
+      <c r="I361" s="0"/>
+      <c r="J361" s="0"/>
+      <c r="K361" s="0"/>
+      <c r="L361" s="0"/>
+      <c r="M361" s="0"/>
+      <c r="N361" s="0"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="0"/>
+      <c r="B362" s="0"/>
+      <c r="C362" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="D362" s="0"/>
+      <c r="E362" s="0"/>
+      <c r="F362" s="0"/>
+      <c r="G362" s="0"/>
+      <c r="H362" s="0"/>
+      <c r="I362" s="0"/>
+      <c r="J362" s="0"/>
+      <c r="K362" s="0"/>
+      <c r="L362" s="0"/>
+      <c r="M362" s="0"/>
+      <c r="N362" s="0"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="B363" s="0">
+        <v>0.25</v>
+      </c>
+      <c r="C363" s="0">
+        <v>0.25</v>
+      </c>
+      <c r="D363" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="E363" s="0"/>
+      <c r="F363" s="0"/>
+      <c r="G363" s="0"/>
+      <c r="H363" s="0"/>
+      <c r="I363" s="0"/>
+      <c r="J363" s="0"/>
+      <c r="K363" s="0"/>
+      <c r="L363" s="0"/>
+      <c r="M363" s="0"/>
+      <c r="N363" s="0"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B364" s="0"/>
+      <c r="C364" s="0"/>
+      <c r="D364" s="0"/>
+      <c r="E364" s="0"/>
+      <c r="F364" s="0"/>
+      <c r="G364" s="0"/>
+      <c r="H364" s="0"/>
+      <c r="I364" s="0"/>
+      <c r="J364" s="0"/>
+      <c r="K364" s="0"/>
+      <c r="L364" s="0"/>
+      <c r="M364" s="0"/>
+      <c r="N364" s="0"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="0"/>
+      <c r="B365" s="0"/>
+      <c r="C365" s="0"/>
+      <c r="D365" s="0"/>
+      <c r="E365" s="0"/>
+      <c r="F365" s="0"/>
+      <c r="G365" s="0"/>
+      <c r="H365" s="0"/>
+      <c r="I365" s="0"/>
+      <c r="J365" s="0"/>
+      <c r="K365" s="0"/>
+      <c r="L365" s="0"/>
+      <c r="M365" s="0"/>
+      <c r="N365" s="0"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="0"/>
+      <c r="B366" s="0"/>
+      <c r="C366" s="0"/>
+      <c r="D366" s="0"/>
+      <c r="E366" s="0"/>
+      <c r="F366" s="0"/>
+      <c r="G366" s="0"/>
+      <c r="H366" s="0"/>
+      <c r="I366" s="0"/>
+      <c r="J366" s="0"/>
+      <c r="K366" s="0"/>
+      <c r="L366" s="0"/>
+      <c r="M366" s="0"/>
+      <c r="N366" s="0"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B367" s="0"/>
+      <c r="C367" s="0"/>
+      <c r="D367" s="0"/>
+      <c r="E367" s="0"/>
+      <c r="F367" s="0"/>
+      <c r="G367" s="0"/>
+      <c r="H367" s="0"/>
+      <c r="I367" s="0"/>
+      <c r="J367" s="0"/>
+      <c r="K367" s="0"/>
+      <c r="L367" s="0"/>
+      <c r="M367" s="0"/>
+      <c r="N367" s="0"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="B368" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="C368" s="0"/>
+      <c r="D368" s="0"/>
+      <c r="E368" s="0"/>
+      <c r="F368" s="0"/>
+      <c r="G368" s="0"/>
+      <c r="H368" s="0"/>
+      <c r="I368" s="0"/>
+      <c r="J368" s="0"/>
+      <c r="K368" s="0"/>
+      <c r="L368" s="0"/>
+      <c r="M368" s="0"/>
+      <c r="N368" s="0"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="B369" s="0">
+        <v>1</v>
+      </c>
+      <c r="C369" s="0"/>
+      <c r="D369" s="0"/>
+      <c r="E369" s="0"/>
+      <c r="F369" s="0"/>
+      <c r="G369" s="0"/>
+      <c r="H369" s="0"/>
+      <c r="I369" s="0"/>
+      <c r="J369" s="0"/>
+      <c r="K369" s="0"/>
+      <c r="L369" s="0"/>
+      <c r="M369" s="0"/>
+      <c r="N369" s="0"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="0"/>
+      <c r="B370" s="0"/>
+      <c r="C370" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="D370" s="0"/>
+      <c r="E370" s="0"/>
+      <c r="F370" s="0"/>
+      <c r="G370" s="0"/>
+      <c r="H370" s="0"/>
+      <c r="I370" s="0"/>
+      <c r="J370" s="0"/>
+      <c r="K370" s="0"/>
+      <c r="L370" s="0"/>
+      <c r="M370" s="0"/>
+      <c r="N370" s="0"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="B371" s="0">
+        <v>20</v>
+      </c>
+      <c r="C371" s="0">
+        <v>10000</v>
+      </c>
+      <c r="D371" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="E371" s="0"/>
+      <c r="F371" s="0"/>
+      <c r="G371" s="0"/>
+      <c r="H371" s="0"/>
+      <c r="I371" s="0"/>
+      <c r="J371" s="0"/>
+      <c r="K371" s="0"/>
+      <c r="L371" s="0"/>
+      <c r="M371" s="0"/>
+      <c r="N371" s="0"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="B372" s="0">
+        <v>0</v>
+      </c>
+      <c r="C372" s="0">
+        <v>0</v>
+      </c>
+      <c r="D372" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="E372" s="0"/>
+      <c r="F372" s="0"/>
+      <c r="G372" s="0"/>
+      <c r="H372" s="0"/>
+      <c r="I372" s="0"/>
+      <c r="J372" s="0"/>
+      <c r="K372" s="0"/>
+      <c r="L372" s="0"/>
+      <c r="M372" s="0"/>
+      <c r="N372" s="0"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="B373" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="C373" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="D373" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="E373" s="0"/>
+      <c r="F373" s="0"/>
+      <c r="G373" s="0"/>
+      <c r="H373" s="0"/>
+      <c r="I373" s="0"/>
+      <c r="J373" s="0"/>
+      <c r="K373" s="0"/>
+      <c r="L373" s="0"/>
+      <c r="M373" s="0"/>
+      <c r="N373" s="0"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="B374" s="0">
+        <v>5</v>
+      </c>
+      <c r="C374" s="0">
+        <v>1</v>
+      </c>
+      <c r="D374" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="E374" s="0"/>
+      <c r="F374" s="0"/>
+      <c r="G374" s="0"/>
+      <c r="H374" s="0"/>
+      <c r="I374" s="0"/>
+      <c r="J374" s="0"/>
+      <c r="K374" s="0"/>
+      <c r="L374" s="0"/>
+      <c r="M374" s="0"/>
+      <c r="N374" s="0"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="B375" s="0">
+        <v>1</v>
+      </c>
+      <c r="C375" s="0">
+        <v>1</v>
+      </c>
+      <c r="D375" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="E375" s="0"/>
+      <c r="F375" s="0"/>
+      <c r="G375" s="0"/>
+      <c r="H375" s="0"/>
+      <c r="I375" s="0"/>
+      <c r="J375" s="0"/>
+      <c r="K375" s="0"/>
+      <c r="L375" s="0"/>
+      <c r="M375" s="0"/>
+      <c r="N375" s="0"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B376" s="0"/>
+      <c r="C376" s="0"/>
+      <c r="D376" s="0"/>
+      <c r="E376" s="0"/>
+      <c r="F376" s="0"/>
+      <c r="G376" s="0"/>
+      <c r="H376" s="0"/>
+      <c r="I376" s="0"/>
+      <c r="J376" s="0"/>
+      <c r="K376" s="0"/>
+      <c r="L376" s="0"/>
+      <c r="M376" s="0"/>
+      <c r="N376" s="0"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="0"/>
+      <c r="B377" s="0"/>
+      <c r="C377" s="0"/>
+      <c r="D377" s="0"/>
+      <c r="E377" s="0"/>
+      <c r="F377" s="0"/>
+      <c r="G377" s="0"/>
+      <c r="H377" s="0"/>
+      <c r="I377" s="0"/>
+      <c r="J377" s="0"/>
+      <c r="K377" s="0"/>
+      <c r="L377" s="0"/>
+      <c r="M377" s="0"/>
+      <c r="N377" s="0"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="0"/>
+      <c r="B378" s="0"/>
+      <c r="C378" s="0"/>
+      <c r="D378" s="0"/>
+      <c r="E378" s="0"/>
+      <c r="F378" s="0"/>
+      <c r="G378" s="0"/>
+      <c r="H378" s="0"/>
+      <c r="I378" s="0"/>
+      <c r="J378" s="0"/>
+      <c r="K378" s="0"/>
+      <c r="L378" s="0"/>
+      <c r="M378" s="0"/>
+      <c r="N378" s="0"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="B379" s="0"/>
+      <c r="C379" s="0"/>
+      <c r="D379" s="0"/>
+      <c r="E379" s="0"/>
+      <c r="F379" s="0"/>
+      <c r="G379" s="0"/>
+      <c r="H379" s="0"/>
+      <c r="I379" s="0"/>
+      <c r="J379" s="0"/>
+      <c r="K379" s="0"/>
+      <c r="L379" s="0"/>
+      <c r="M379" s="0"/>
+      <c r="N379" s="0"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="B380" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="C380" s="0"/>
+      <c r="D380" s="0"/>
+      <c r="E380" s="0"/>
+      <c r="F380" s="0"/>
+      <c r="G380" s="0"/>
+      <c r="H380" s="0"/>
+      <c r="I380" s="0"/>
+      <c r="J380" s="0"/>
+      <c r="K380" s="0"/>
+      <c r="L380" s="0"/>
+      <c r="M380" s="0"/>
+      <c r="N380" s="0"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="B381" s="0">
+        <v>1</v>
+      </c>
+      <c r="C381" s="0"/>
+      <c r="D381" s="0"/>
+      <c r="E381" s="0"/>
+      <c r="F381" s="0"/>
+      <c r="G381" s="0"/>
+      <c r="H381" s="0"/>
+      <c r="I381" s="0"/>
+      <c r="J381" s="0"/>
+      <c r="K381" s="0"/>
+      <c r="L381" s="0"/>
+      <c r="M381" s="0"/>
+      <c r="N381" s="0"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="B382" s="0">
+        <v>3034</v>
+      </c>
+      <c r="C382" s="0"/>
+      <c r="D382" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="E382" s="0"/>
+      <c r="F382" s="0"/>
+      <c r="G382" s="0"/>
+      <c r="H382" s="0"/>
+      <c r="I382" s="0"/>
+      <c r="J382" s="0"/>
+      <c r="K382" s="0"/>
+      <c r="L382" s="0"/>
+      <c r="M382" s="0"/>
+      <c r="N382" s="0"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="B383" s="0"/>
+      <c r="C383" s="0"/>
+      <c r="D383" s="0"/>
+      <c r="E383" s="0"/>
+      <c r="F383" s="0"/>
+      <c r="G383" s="0"/>
+      <c r="H383" s="0"/>
+      <c r="I383" s="0"/>
+      <c r="J383" s="0"/>
+      <c r="K383" s="0"/>
+      <c r="L383" s="0"/>
+      <c r="M383" s="0"/>
+      <c r="N383" s="0"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="B384" s="0">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="C384" s="0"/>
+      <c r="D384" s="0"/>
+      <c r="E384" s="0"/>
+      <c r="F384" s="0"/>
+      <c r="G384" s="0"/>
+      <c r="H384" s="0"/>
+      <c r="I384" s="0"/>
+      <c r="J384" s="0"/>
+      <c r="K384" s="0"/>
+      <c r="L384" s="0"/>
+      <c r="M384" s="0"/>
+      <c r="N384" s="0"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="B385" s="0">
+        <v>50</v>
+      </c>
+      <c r="C385" s="0"/>
+      <c r="D385" s="0"/>
+      <c r="E385" s="0"/>
+      <c r="F385" s="0"/>
+      <c r="G385" s="0"/>
+      <c r="H385" s="0"/>
+      <c r="I385" s="0"/>
+      <c r="J385" s="0"/>
+      <c r="K385" s="0"/>
+      <c r="L385" s="0"/>
+      <c r="M385" s="0"/>
+      <c r="N385" s="0"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="B386" s="0">
+        <v>1</v>
+      </c>
+      <c r="C386" s="0"/>
+      <c r="D386" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="E386" s="0"/>
+      <c r="F386" s="0"/>
+      <c r="G386" s="0"/>
+      <c r="H386" s="0"/>
+      <c r="I386" s="0"/>
+      <c r="J386" s="0"/>
+      <c r="K386" s="0"/>
+      <c r="L386" s="0"/>
+      <c r="M386" s="0"/>
+      <c r="N386" s="0"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B387" s="0"/>
+      <c r="C387" s="0"/>
+      <c r="D387" s="0"/>
+      <c r="E387" s="0"/>
+      <c r="F387" s="0"/>
+      <c r="G387" s="0"/>
+      <c r="H387" s="0"/>
+      <c r="I387" s="0"/>
+      <c r="J387" s="0"/>
+      <c r="K387" s="0"/>
+      <c r="L387" s="0"/>
+      <c r="M387" s="0"/>
+      <c r="N387" s="0"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="0"/>
+      <c r="B388" s="0"/>
+      <c r="C388" s="0"/>
+      <c r="D388" s="0"/>
+      <c r="E388" s="0"/>
+      <c r="F388" s="0"/>
+      <c r="G388" s="0"/>
+      <c r="H388" s="0"/>
+      <c r="I388" s="0"/>
+      <c r="J388" s="0"/>
+      <c r="K388" s="0"/>
+      <c r="L388" s="0"/>
+      <c r="M388" s="0"/>
+      <c r="N388" s="0"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="0"/>
+      <c r="B389" s="0"/>
+      <c r="C389" s="0"/>
+      <c r="D389" s="0"/>
+      <c r="E389" s="0"/>
+      <c r="F389" s="0"/>
+      <c r="G389" s="0"/>
+      <c r="H389" s="0"/>
+      <c r="I389" s="0"/>
+      <c r="J389" s="0"/>
+      <c r="K389" s="0"/>
+      <c r="L389" s="0"/>
+      <c r="M389" s="0"/>
+      <c r="N389" s="0"/>
     </row>
   </sheetData>
 </worksheet>
